--- a/model performance comparison/Ratio_Cfree_Cnominal/Nicol_data/Fischer model_MCF7.xlsx
+++ b/model performance comparison/Ratio_Cfree_Cnominal/Nicol_data/Fischer model_MCF7.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TAMU PHD\MassBalance project\Validation_Unilever\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TAMU PHD\MassBalance project\Paper writing\R1\model comparison_update_based reviewer\Validation_Unilever\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBB036FF-0285-451F-B7EC-0B280A2998D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4EFEDE4-1B33-4FC1-9E56-D1F0CEF8B453}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43080" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Model structure" sheetId="1" r:id="rId1"/>
@@ -428,7 +428,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="140">
   <si>
     <t>Assumptions:</t>
   </si>
@@ -2042,6 +2042,143 @@
     <xf numFmtId="0" fontId="14" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
@@ -2129,12 +2266,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2161,137 +2292,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="12" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -14096,8 +14096,8 @@
       <c r="D1" s="7"/>
       <c r="E1" s="7"/>
       <c r="F1" s="7"/>
-      <c r="G1" s="155"/>
-      <c r="H1" s="155"/>
+      <c r="G1" s="125"/>
+      <c r="H1" s="125"/>
       <c r="I1" s="7"/>
       <c r="J1" s="7"/>
       <c r="K1" s="7"/>
@@ -14130,19 +14130,19 @@
       <c r="D2" s="7"/>
       <c r="E2" s="7"/>
       <c r="F2" s="7"/>
-      <c r="G2" s="155"/>
-      <c r="H2" s="155"/>
-      <c r="I2" s="100" t="s">
+      <c r="G2" s="125"/>
+      <c r="H2" s="125"/>
+      <c r="I2" s="138" t="s">
         <v>20</v>
       </c>
-      <c r="J2" s="101"/>
-      <c r="K2" s="101"/>
-      <c r="L2" s="101"/>
-      <c r="M2" s="101"/>
-      <c r="N2" s="101"/>
-      <c r="O2" s="101"/>
-      <c r="P2" s="101"/>
-      <c r="Q2" s="102"/>
+      <c r="J2" s="139"/>
+      <c r="K2" s="139"/>
+      <c r="L2" s="139"/>
+      <c r="M2" s="139"/>
+      <c r="N2" s="139"/>
+      <c r="O2" s="139"/>
+      <c r="P2" s="139"/>
+      <c r="Q2" s="140"/>
       <c r="R2" s="7"/>
       <c r="S2" s="7"/>
       <c r="T2" s="7"/>
@@ -14166,17 +14166,17 @@
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
       <c r="F3" s="7"/>
-      <c r="G3" s="155"/>
-      <c r="H3" s="155"/>
-      <c r="I3" s="103"/>
-      <c r="J3" s="104"/>
-      <c r="K3" s="104"/>
-      <c r="L3" s="104"/>
-      <c r="M3" s="104"/>
-      <c r="N3" s="104"/>
-      <c r="O3" s="104"/>
-      <c r="P3" s="104"/>
-      <c r="Q3" s="105"/>
+      <c r="G3" s="125"/>
+      <c r="H3" s="125"/>
+      <c r="I3" s="141"/>
+      <c r="J3" s="142"/>
+      <c r="K3" s="142"/>
+      <c r="L3" s="142"/>
+      <c r="M3" s="142"/>
+      <c r="N3" s="142"/>
+      <c r="O3" s="142"/>
+      <c r="P3" s="142"/>
+      <c r="Q3" s="143"/>
       <c r="R3" s="7"/>
       <c r="S3" s="7"/>
       <c r="T3" s="7"/>
@@ -14200,17 +14200,17 @@
       <c r="D4" s="7"/>
       <c r="E4" s="7"/>
       <c r="F4" s="7"/>
-      <c r="G4" s="155"/>
-      <c r="H4" s="155"/>
-      <c r="I4" s="106"/>
-      <c r="J4" s="107"/>
-      <c r="K4" s="107"/>
-      <c r="L4" s="107"/>
-      <c r="M4" s="107"/>
-      <c r="N4" s="107"/>
-      <c r="O4" s="107"/>
-      <c r="P4" s="107"/>
-      <c r="Q4" s="108"/>
+      <c r="G4" s="125"/>
+      <c r="H4" s="125"/>
+      <c r="I4" s="144"/>
+      <c r="J4" s="145"/>
+      <c r="K4" s="145"/>
+      <c r="L4" s="145"/>
+      <c r="M4" s="145"/>
+      <c r="N4" s="145"/>
+      <c r="O4" s="145"/>
+      <c r="P4" s="145"/>
+      <c r="Q4" s="146"/>
       <c r="R4" s="7"/>
       <c r="S4" s="7"/>
       <c r="T4" s="7"/>
@@ -14234,19 +14234,19 @@
       <c r="D5" s="7"/>
       <c r="E5" s="7"/>
       <c r="F5" s="7"/>
-      <c r="G5" s="155"/>
-      <c r="H5" s="155"/>
-      <c r="I5" s="109" t="s">
+      <c r="G5" s="125"/>
+      <c r="H5" s="125"/>
+      <c r="I5" s="147" t="s">
         <v>40</v>
       </c>
-      <c r="J5" s="110"/>
-      <c r="K5" s="110"/>
-      <c r="L5" s="110"/>
-      <c r="M5" s="110"/>
-      <c r="N5" s="110"/>
-      <c r="O5" s="110"/>
-      <c r="P5" s="110"/>
-      <c r="Q5" s="111"/>
+      <c r="J5" s="148"/>
+      <c r="K5" s="148"/>
+      <c r="L5" s="148"/>
+      <c r="M5" s="148"/>
+      <c r="N5" s="148"/>
+      <c r="O5" s="148"/>
+      <c r="P5" s="148"/>
+      <c r="Q5" s="149"/>
       <c r="R5" s="7"/>
       <c r="S5" s="7"/>
       <c r="T5" s="7"/>
@@ -14270,8 +14270,8 @@
       <c r="D6" s="7"/>
       <c r="E6" s="7"/>
       <c r="F6" s="7"/>
-      <c r="G6" s="155"/>
-      <c r="H6" s="155"/>
+      <c r="G6" s="125"/>
+      <c r="H6" s="125"/>
       <c r="I6" s="50" t="s">
         <v>51</v>
       </c>
@@ -14281,14 +14281,14 @@
       <c r="K6" s="50" t="s">
         <v>48</v>
       </c>
-      <c r="L6" s="152" t="s">
+      <c r="L6" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="M6" s="153"/>
-      <c r="N6" s="153"/>
-      <c r="O6" s="153"/>
-      <c r="P6" s="153"/>
-      <c r="Q6" s="154"/>
+      <c r="M6" s="118"/>
+      <c r="N6" s="118"/>
+      <c r="O6" s="118"/>
+      <c r="P6" s="118"/>
+      <c r="Q6" s="119"/>
       <c r="R6" s="7"/>
       <c r="S6" s="7"/>
       <c r="T6" s="7"/>
@@ -14312,8 +14312,8 @@
       <c r="D7" s="7"/>
       <c r="E7" s="7"/>
       <c r="F7" s="7"/>
-      <c r="G7" s="155"/>
-      <c r="H7" s="155"/>
+      <c r="G7" s="125"/>
+      <c r="H7" s="125"/>
       <c r="I7" s="51" t="s">
         <v>21</v>
       </c>
@@ -14325,14 +14325,14 @@
         <f>J7/J7</f>
         <v>1</v>
       </c>
-      <c r="L7" s="146" t="s">
+      <c r="L7" s="100" t="s">
         <v>70</v>
       </c>
-      <c r="M7" s="147"/>
-      <c r="N7" s="147"/>
-      <c r="O7" s="147"/>
-      <c r="P7" s="147"/>
-      <c r="Q7" s="148"/>
+      <c r="M7" s="101"/>
+      <c r="N7" s="101"/>
+      <c r="O7" s="101"/>
+      <c r="P7" s="101"/>
+      <c r="Q7" s="102"/>
       <c r="R7" s="7"/>
       <c r="S7" s="7"/>
       <c r="T7" s="7"/>
@@ -14351,15 +14351,15 @@
     </row>
     <row r="8" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A8" s="7"/>
-      <c r="B8" s="127" t="s">
+      <c r="B8" s="163" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="128"/>
-      <c r="D8" s="128"/>
-      <c r="E8" s="128"/>
-      <c r="F8" s="129"/>
-      <c r="G8" s="155"/>
-      <c r="H8" s="155"/>
+      <c r="C8" s="164"/>
+      <c r="D8" s="164"/>
+      <c r="E8" s="164"/>
+      <c r="F8" s="165"/>
+      <c r="G8" s="125"/>
+      <c r="H8" s="125"/>
       <c r="I8" s="52" t="s">
         <v>6</v>
       </c>
@@ -14371,14 +14371,14 @@
         <f>J8/J7</f>
         <v>0.99452376657824937</v>
       </c>
-      <c r="L8" s="146" t="s">
+      <c r="L8" s="100" t="s">
         <v>71</v>
       </c>
-      <c r="M8" s="147"/>
-      <c r="N8" s="147"/>
-      <c r="O8" s="147"/>
-      <c r="P8" s="147"/>
-      <c r="Q8" s="148"/>
+      <c r="M8" s="101"/>
+      <c r="N8" s="101"/>
+      <c r="O8" s="101"/>
+      <c r="P8" s="101"/>
+      <c r="Q8" s="102"/>
       <c r="R8" s="7"/>
       <c r="S8" s="7"/>
       <c r="T8" s="7"/>
@@ -14397,13 +14397,13 @@
     </row>
     <row r="9" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" s="7"/>
-      <c r="B9" s="130"/>
-      <c r="C9" s="131"/>
-      <c r="D9" s="131"/>
-      <c r="E9" s="131"/>
-      <c r="F9" s="132"/>
-      <c r="G9" s="155"/>
-      <c r="H9" s="155"/>
+      <c r="B9" s="166"/>
+      <c r="C9" s="167"/>
+      <c r="D9" s="167"/>
+      <c r="E9" s="167"/>
+      <c r="F9" s="168"/>
+      <c r="G9" s="125"/>
+      <c r="H9" s="125"/>
       <c r="I9" s="51" t="s">
         <v>8</v>
       </c>
@@ -14415,14 +14415,14 @@
         <f>J9/J7</f>
         <v>5.3179840848806368E-3</v>
       </c>
-      <c r="L9" s="146" t="s">
+      <c r="L9" s="100" t="s">
         <v>71</v>
       </c>
-      <c r="M9" s="147"/>
-      <c r="N9" s="147"/>
-      <c r="O9" s="147"/>
-      <c r="P9" s="147"/>
-      <c r="Q9" s="148"/>
+      <c r="M9" s="101"/>
+      <c r="N9" s="101"/>
+      <c r="O9" s="101"/>
+      <c r="P9" s="101"/>
+      <c r="Q9" s="102"/>
       <c r="R9" s="7"/>
       <c r="S9" s="7"/>
       <c r="T9" s="7"/>
@@ -14441,13 +14441,13 @@
     </row>
     <row r="10" spans="1:32" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A10" s="7"/>
-      <c r="B10" s="133"/>
-      <c r="C10" s="134"/>
-      <c r="D10" s="134"/>
-      <c r="E10" s="134"/>
-      <c r="F10" s="135"/>
-      <c r="G10" s="155"/>
-      <c r="H10" s="155"/>
+      <c r="B10" s="169"/>
+      <c r="C10" s="170"/>
+      <c r="D10" s="170"/>
+      <c r="E10" s="170"/>
+      <c r="F10" s="171"/>
+      <c r="G10" s="125"/>
+      <c r="H10" s="125"/>
       <c r="I10" s="52" t="s">
         <v>9</v>
       </c>
@@ -14459,14 +14459,14 @@
         <f>J10/J7</f>
         <v>1.5824933687002654E-4</v>
       </c>
-      <c r="L10" s="146" t="s">
+      <c r="L10" s="100" t="s">
         <v>71</v>
       </c>
-      <c r="M10" s="147"/>
-      <c r="N10" s="147"/>
-      <c r="O10" s="147"/>
-      <c r="P10" s="147"/>
-      <c r="Q10" s="148"/>
+      <c r="M10" s="101"/>
+      <c r="N10" s="101"/>
+      <c r="O10" s="101"/>
+      <c r="P10" s="101"/>
+      <c r="Q10" s="102"/>
       <c r="R10" s="7"/>
       <c r="S10" s="7"/>
       <c r="T10" s="7"/>
@@ -14485,24 +14485,24 @@
     </row>
     <row r="11" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="7"/>
-      <c r="B11" s="136" t="s">
+      <c r="B11" s="128" t="s">
         <v>38</v>
       </c>
-      <c r="C11" s="137"/>
-      <c r="D11" s="137"/>
-      <c r="E11" s="137"/>
-      <c r="F11" s="138"/>
-      <c r="G11" s="155"/>
-      <c r="H11" s="155"/>
-      <c r="I11" s="171"/>
-      <c r="J11" s="171"/>
-      <c r="K11" s="171"/>
-      <c r="L11" s="171"/>
-      <c r="M11" s="171"/>
-      <c r="N11" s="171"/>
-      <c r="O11" s="171"/>
-      <c r="P11" s="171"/>
-      <c r="Q11" s="171"/>
+      <c r="C11" s="129"/>
+      <c r="D11" s="129"/>
+      <c r="E11" s="129"/>
+      <c r="F11" s="130"/>
+      <c r="G11" s="125"/>
+      <c r="H11" s="125"/>
+      <c r="I11" s="116"/>
+      <c r="J11" s="116"/>
+      <c r="K11" s="116"/>
+      <c r="L11" s="116"/>
+      <c r="M11" s="116"/>
+      <c r="N11" s="116"/>
+      <c r="O11" s="116"/>
+      <c r="P11" s="116"/>
+      <c r="Q11" s="116"/>
       <c r="R11" s="7"/>
       <c r="S11" s="7"/>
       <c r="T11" s="7"/>
@@ -14521,13 +14521,13 @@
     </row>
     <row r="12" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="7"/>
-      <c r="B12" s="139"/>
-      <c r="C12" s="140"/>
-      <c r="D12" s="140"/>
-      <c r="E12" s="140"/>
-      <c r="F12" s="141"/>
-      <c r="G12" s="155"/>
-      <c r="H12" s="155"/>
+      <c r="B12" s="131"/>
+      <c r="C12" s="132"/>
+      <c r="D12" s="132"/>
+      <c r="E12" s="132"/>
+      <c r="F12" s="133"/>
+      <c r="G12" s="125"/>
+      <c r="H12" s="125"/>
       <c r="I12" s="50" t="s">
         <v>53</v>
       </c>
@@ -14537,14 +14537,14 @@
       <c r="K12" s="50" t="s">
         <v>48</v>
       </c>
-      <c r="L12" s="152" t="s">
+      <c r="L12" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="M12" s="153"/>
-      <c r="N12" s="153"/>
-      <c r="O12" s="153"/>
-      <c r="P12" s="153"/>
-      <c r="Q12" s="154"/>
+      <c r="M12" s="118"/>
+      <c r="N12" s="118"/>
+      <c r="O12" s="118"/>
+      <c r="P12" s="118"/>
+      <c r="Q12" s="119"/>
       <c r="R12" s="7"/>
       <c r="S12" s="7"/>
       <c r="T12" s="7"/>
@@ -14563,17 +14563,17 @@
     </row>
     <row r="13" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A13" s="8"/>
-      <c r="B13" s="125" t="s">
+      <c r="B13" s="120" t="s">
         <v>4</v>
       </c>
-      <c r="C13" s="126"/>
-      <c r="D13" s="115" t="s">
+      <c r="C13" s="121"/>
+      <c r="D13" s="153" t="s">
         <v>41</v>
       </c>
-      <c r="E13" s="115"/>
-      <c r="F13" s="115"/>
-      <c r="G13" s="155"/>
-      <c r="H13" s="155"/>
+      <c r="E13" s="153"/>
+      <c r="F13" s="153"/>
+      <c r="G13" s="125"/>
+      <c r="H13" s="125"/>
       <c r="I13" s="51" t="s">
         <v>5</v>
       </c>
@@ -14585,14 +14585,14 @@
         <f>J13/J13</f>
         <v>1</v>
       </c>
-      <c r="L13" s="146" t="s">
+      <c r="L13" s="100" t="s">
         <v>73</v>
       </c>
-      <c r="M13" s="147"/>
-      <c r="N13" s="147"/>
-      <c r="O13" s="147"/>
-      <c r="P13" s="147"/>
-      <c r="Q13" s="148"/>
+      <c r="M13" s="101"/>
+      <c r="N13" s="101"/>
+      <c r="O13" s="101"/>
+      <c r="P13" s="101"/>
+      <c r="Q13" s="102"/>
       <c r="R13" s="7"/>
       <c r="S13" s="7"/>
       <c r="T13" s="7"/>
@@ -14617,13 +14617,13 @@
       <c r="C14" s="44">
         <v>300</v>
       </c>
-      <c r="D14" s="116" t="s">
+      <c r="D14" s="154" t="s">
         <v>18</v>
       </c>
-      <c r="E14" s="116"/>
-      <c r="F14" s="116"/>
-      <c r="G14" s="155"/>
-      <c r="H14" s="155"/>
+      <c r="E14" s="154"/>
+      <c r="F14" s="154"/>
+      <c r="G14" s="125"/>
+      <c r="H14" s="125"/>
       <c r="I14" s="52" t="s">
         <v>45</v>
       </c>
@@ -14635,14 +14635,14 @@
         <f>J14/J13</f>
         <v>0.99452376657824937</v>
       </c>
-      <c r="L14" s="149" t="s">
+      <c r="L14" s="122" t="s">
         <v>72</v>
       </c>
-      <c r="M14" s="150"/>
-      <c r="N14" s="150"/>
-      <c r="O14" s="150"/>
-      <c r="P14" s="150"/>
-      <c r="Q14" s="151"/>
+      <c r="M14" s="123"/>
+      <c r="N14" s="123"/>
+      <c r="O14" s="123"/>
+      <c r="P14" s="123"/>
+      <c r="Q14" s="124"/>
       <c r="R14" s="7"/>
       <c r="S14" s="7"/>
       <c r="T14" s="7"/>
@@ -14667,13 +14667,13 @@
       <c r="C15" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="D15" s="117" t="s">
+      <c r="D15" s="155" t="s">
         <v>62</v>
       </c>
-      <c r="E15" s="117"/>
-      <c r="F15" s="117"/>
-      <c r="G15" s="155"/>
-      <c r="H15" s="155"/>
+      <c r="E15" s="155"/>
+      <c r="F15" s="155"/>
+      <c r="G15" s="125"/>
+      <c r="H15" s="125"/>
       <c r="I15" s="51" t="s">
         <v>46</v>
       </c>
@@ -14685,14 +14685,14 @@
         <f>J15/J13</f>
         <v>5.3179840848806368E-3</v>
       </c>
-      <c r="L15" s="146" t="s">
+      <c r="L15" s="100" t="s">
         <v>71</v>
       </c>
-      <c r="M15" s="147"/>
-      <c r="N15" s="147"/>
-      <c r="O15" s="147"/>
-      <c r="P15" s="147"/>
-      <c r="Q15" s="148"/>
+      <c r="M15" s="101"/>
+      <c r="N15" s="101"/>
+      <c r="O15" s="101"/>
+      <c r="P15" s="101"/>
+      <c r="Q15" s="102"/>
       <c r="R15" s="7"/>
       <c r="S15" s="7"/>
       <c r="T15" s="7"/>
@@ -14718,13 +14718,13 @@
         <f>1-C18</f>
         <v>0.89920424403183019</v>
       </c>
-      <c r="D16" s="118" t="s">
+      <c r="D16" s="156" t="s">
         <v>42</v>
       </c>
-      <c r="E16" s="119"/>
-      <c r="F16" s="120"/>
-      <c r="G16" s="155"/>
-      <c r="H16" s="155"/>
+      <c r="E16" s="157"/>
+      <c r="F16" s="158"/>
+      <c r="G16" s="125"/>
+      <c r="H16" s="125"/>
       <c r="I16" s="52" t="s">
         <v>47</v>
       </c>
@@ -14736,14 +14736,14 @@
         <f>J16/J13</f>
         <v>1.5824933687002654E-4</v>
       </c>
-      <c r="L16" s="146" t="s">
+      <c r="L16" s="100" t="s">
         <v>71</v>
       </c>
-      <c r="M16" s="147"/>
-      <c r="N16" s="147"/>
-      <c r="O16" s="147"/>
-      <c r="P16" s="147"/>
-      <c r="Q16" s="148"/>
+      <c r="M16" s="101"/>
+      <c r="N16" s="101"/>
+      <c r="O16" s="101"/>
+      <c r="P16" s="101"/>
+      <c r="Q16" s="102"/>
       <c r="R16" s="7"/>
       <c r="S16" s="7"/>
       <c r="T16" s="7"/>
@@ -14768,22 +14768,22 @@
       <c r="C17" s="44" t="s">
         <v>78</v>
       </c>
-      <c r="D17" s="121" t="s">
+      <c r="D17" s="159" t="s">
         <v>63</v>
       </c>
-      <c r="E17" s="122"/>
-      <c r="F17" s="123"/>
-      <c r="G17" s="155"/>
-      <c r="H17" s="155"/>
-      <c r="I17" s="149"/>
-      <c r="J17" s="150"/>
-      <c r="K17" s="150"/>
-      <c r="L17" s="150"/>
-      <c r="M17" s="150"/>
-      <c r="N17" s="150"/>
-      <c r="O17" s="150"/>
-      <c r="P17" s="150"/>
-      <c r="Q17" s="151"/>
+      <c r="E17" s="160"/>
+      <c r="F17" s="161"/>
+      <c r="G17" s="125"/>
+      <c r="H17" s="125"/>
+      <c r="I17" s="122"/>
+      <c r="J17" s="123"/>
+      <c r="K17" s="123"/>
+      <c r="L17" s="123"/>
+      <c r="M17" s="123"/>
+      <c r="N17" s="123"/>
+      <c r="O17" s="123"/>
+      <c r="P17" s="123"/>
+      <c r="Q17" s="124"/>
       <c r="R17" s="7"/>
       <c r="S17" s="7"/>
       <c r="T17" s="7"/>
@@ -14808,13 +14808,13 @@
       <c r="C18" s="45">
         <v>0.10079575596816977</v>
       </c>
-      <c r="D18" s="118" t="s">
+      <c r="D18" s="156" t="s">
         <v>43</v>
       </c>
-      <c r="E18" s="119"/>
-      <c r="F18" s="120"/>
-      <c r="G18" s="155"/>
-      <c r="H18" s="155"/>
+      <c r="E18" s="157"/>
+      <c r="F18" s="158"/>
+      <c r="G18" s="125"/>
+      <c r="H18" s="125"/>
       <c r="I18" s="50" t="s">
         <v>31</v>
       </c>
@@ -14824,14 +14824,14 @@
       <c r="K18" s="50" t="s">
         <v>48</v>
       </c>
-      <c r="L18" s="152" t="s">
+      <c r="L18" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="M18" s="153"/>
-      <c r="N18" s="153"/>
-      <c r="O18" s="153"/>
-      <c r="P18" s="153"/>
-      <c r="Q18" s="154"/>
+      <c r="M18" s="118"/>
+      <c r="N18" s="118"/>
+      <c r="O18" s="118"/>
+      <c r="P18" s="118"/>
+      <c r="Q18" s="119"/>
       <c r="R18" s="7"/>
       <c r="S18" s="7"/>
       <c r="T18" s="7"/>
@@ -14850,13 +14850,13 @@
     </row>
     <row r="19" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A19" s="7"/>
-      <c r="B19" s="117"/>
-      <c r="C19" s="117"/>
-      <c r="D19" s="117"/>
-      <c r="E19" s="117"/>
-      <c r="F19" s="117"/>
-      <c r="G19" s="155"/>
-      <c r="H19" s="155"/>
+      <c r="B19" s="155"/>
+      <c r="C19" s="155"/>
+      <c r="D19" s="155"/>
+      <c r="E19" s="155"/>
+      <c r="F19" s="155"/>
+      <c r="G19" s="125"/>
+      <c r="H19" s="125"/>
       <c r="I19" s="51" t="s">
         <v>5</v>
       </c>
@@ -14868,14 +14868,14 @@
         <f>J19/J19</f>
         <v>1</v>
       </c>
-      <c r="L19" s="146" t="s">
+      <c r="L19" s="100" t="s">
         <v>57</v>
       </c>
-      <c r="M19" s="147"/>
-      <c r="N19" s="147"/>
-      <c r="O19" s="147"/>
-      <c r="P19" s="147"/>
-      <c r="Q19" s="148"/>
+      <c r="M19" s="101"/>
+      <c r="N19" s="101"/>
+      <c r="O19" s="101"/>
+      <c r="P19" s="101"/>
+      <c r="Q19" s="102"/>
       <c r="R19" s="7"/>
       <c r="S19" s="7"/>
       <c r="T19" s="7"/>
@@ -14894,17 +14894,17 @@
     </row>
     <row r="20" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A20" s="7"/>
-      <c r="B20" s="125" t="s">
+      <c r="B20" s="120" t="s">
         <v>7</v>
       </c>
-      <c r="C20" s="126"/>
-      <c r="D20" s="115" t="s">
+      <c r="C20" s="121"/>
+      <c r="D20" s="153" t="s">
         <v>41</v>
       </c>
-      <c r="E20" s="115"/>
-      <c r="F20" s="115"/>
-      <c r="G20" s="155"/>
-      <c r="H20" s="155"/>
+      <c r="E20" s="153"/>
+      <c r="F20" s="153"/>
+      <c r="G20" s="125"/>
+      <c r="H20" s="125"/>
       <c r="I20" s="52" t="s">
         <v>45</v>
       </c>
@@ -14916,14 +14916,14 @@
         <f>J20/J19</f>
         <v>0.88409626092573368</v>
       </c>
-      <c r="L20" s="146" t="s">
+      <c r="L20" s="100" t="s">
         <v>71</v>
       </c>
-      <c r="M20" s="147"/>
-      <c r="N20" s="147"/>
-      <c r="O20" s="147"/>
-      <c r="P20" s="147"/>
-      <c r="Q20" s="148"/>
+      <c r="M20" s="101"/>
+      <c r="N20" s="101"/>
+      <c r="O20" s="101"/>
+      <c r="P20" s="101"/>
+      <c r="Q20" s="102"/>
       <c r="R20" s="7"/>
       <c r="S20" s="7"/>
       <c r="T20" s="7"/>
@@ -14948,13 +14948,13 @@
       <c r="C21" s="44" t="s">
         <v>139</v>
       </c>
-      <c r="D21" s="121" t="s">
+      <c r="D21" s="159" t="s">
         <v>63</v>
       </c>
-      <c r="E21" s="122"/>
-      <c r="F21" s="123"/>
-      <c r="G21" s="155"/>
-      <c r="H21" s="155"/>
+      <c r="E21" s="160"/>
+      <c r="F21" s="161"/>
+      <c r="G21" s="125"/>
+      <c r="H21" s="125"/>
       <c r="I21" s="51" t="s">
         <v>46</v>
       </c>
@@ -14966,14 +14966,14 @@
         <f>J21/J19</f>
         <v>9.3424732018020817E-2</v>
       </c>
-      <c r="L21" s="146" t="s">
+      <c r="L21" s="100" t="s">
         <v>71</v>
       </c>
-      <c r="M21" s="147"/>
-      <c r="N21" s="147"/>
-      <c r="O21" s="147"/>
-      <c r="P21" s="147"/>
-      <c r="Q21" s="148"/>
+      <c r="M21" s="101"/>
+      <c r="N21" s="101"/>
+      <c r="O21" s="101"/>
+      <c r="P21" s="101"/>
+      <c r="Q21" s="102"/>
       <c r="R21" s="7"/>
       <c r="S21" s="7"/>
       <c r="T21" s="7"/>
@@ -14998,13 +14998,13 @@
       <c r="C22" s="46">
         <v>1.0000000000000001E-30</v>
       </c>
-      <c r="D22" s="124" t="s">
+      <c r="D22" s="162" t="s">
         <v>69</v>
       </c>
-      <c r="E22" s="124"/>
-      <c r="F22" s="124"/>
-      <c r="G22" s="155"/>
-      <c r="H22" s="155"/>
+      <c r="E22" s="162"/>
+      <c r="F22" s="162"/>
+      <c r="G22" s="125"/>
+      <c r="H22" s="125"/>
       <c r="I22" s="53" t="s">
         <v>47</v>
       </c>
@@ -15016,14 +15016,14 @@
         <f>J22/J19</f>
         <v>2.2479007056245552E-2</v>
       </c>
-      <c r="L22" s="146" t="s">
+      <c r="L22" s="100" t="s">
         <v>71</v>
       </c>
-      <c r="M22" s="147"/>
-      <c r="N22" s="147"/>
-      <c r="O22" s="147"/>
-      <c r="P22" s="147"/>
-      <c r="Q22" s="148"/>
+      <c r="M22" s="101"/>
+      <c r="N22" s="101"/>
+      <c r="O22" s="101"/>
+      <c r="P22" s="101"/>
+      <c r="Q22" s="102"/>
       <c r="R22" s="7"/>
       <c r="S22" s="7"/>
       <c r="T22" s="7"/>
@@ -15042,22 +15042,22 @@
     </row>
     <row r="23" spans="1:32" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A23" s="7"/>
-      <c r="B23" s="112"/>
-      <c r="C23" s="113"/>
-      <c r="D23" s="113"/>
-      <c r="E23" s="113"/>
-      <c r="F23" s="114"/>
-      <c r="G23" s="155"/>
-      <c r="H23" s="155"/>
-      <c r="I23" s="166"/>
-      <c r="J23" s="167"/>
-      <c r="K23" s="167"/>
-      <c r="L23" s="167"/>
-      <c r="M23" s="167"/>
-      <c r="N23" s="167"/>
-      <c r="O23" s="167"/>
-      <c r="P23" s="167"/>
-      <c r="Q23" s="168"/>
+      <c r="B23" s="150"/>
+      <c r="C23" s="151"/>
+      <c r="D23" s="151"/>
+      <c r="E23" s="151"/>
+      <c r="F23" s="152"/>
+      <c r="G23" s="125"/>
+      <c r="H23" s="125"/>
+      <c r="I23" s="111"/>
+      <c r="J23" s="112"/>
+      <c r="K23" s="112"/>
+      <c r="L23" s="112"/>
+      <c r="M23" s="112"/>
+      <c r="N23" s="112"/>
+      <c r="O23" s="112"/>
+      <c r="P23" s="112"/>
+      <c r="Q23" s="113"/>
       <c r="R23" s="7"/>
       <c r="S23" s="7"/>
       <c r="T23" s="7"/>
@@ -15076,26 +15076,26 @@
     </row>
     <row r="24" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A24" s="7"/>
-      <c r="B24" s="136" t="s">
+      <c r="B24" s="128" t="s">
         <v>39</v>
       </c>
-      <c r="C24" s="137"/>
-      <c r="D24" s="137"/>
-      <c r="E24" s="137"/>
-      <c r="F24" s="138"/>
-      <c r="G24" s="155"/>
-      <c r="H24" s="155"/>
-      <c r="I24" s="160" t="s">
+      <c r="C24" s="129"/>
+      <c r="D24" s="129"/>
+      <c r="E24" s="129"/>
+      <c r="F24" s="130"/>
+      <c r="G24" s="125"/>
+      <c r="H24" s="125"/>
+      <c r="I24" s="105" t="s">
         <v>44</v>
       </c>
-      <c r="J24" s="161"/>
-      <c r="K24" s="161"/>
-      <c r="L24" s="161"/>
-      <c r="M24" s="161"/>
-      <c r="N24" s="161"/>
-      <c r="O24" s="161"/>
-      <c r="P24" s="161"/>
-      <c r="Q24" s="162"/>
+      <c r="J24" s="106"/>
+      <c r="K24" s="106"/>
+      <c r="L24" s="106"/>
+      <c r="M24" s="106"/>
+      <c r="N24" s="106"/>
+      <c r="O24" s="106"/>
+      <c r="P24" s="106"/>
+      <c r="Q24" s="107"/>
       <c r="R24" s="7"/>
       <c r="S24" s="7"/>
       <c r="T24" s="7"/>
@@ -15114,22 +15114,22 @@
     </row>
     <row r="25" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A25" s="7"/>
-      <c r="B25" s="139"/>
-      <c r="C25" s="140"/>
-      <c r="D25" s="140"/>
-      <c r="E25" s="140"/>
-      <c r="F25" s="141"/>
-      <c r="G25" s="155"/>
-      <c r="H25" s="155"/>
-      <c r="I25" s="163"/>
-      <c r="J25" s="164"/>
-      <c r="K25" s="164"/>
-      <c r="L25" s="164"/>
-      <c r="M25" s="164"/>
-      <c r="N25" s="164"/>
-      <c r="O25" s="164"/>
-      <c r="P25" s="164"/>
-      <c r="Q25" s="165"/>
+      <c r="B25" s="131"/>
+      <c r="C25" s="132"/>
+      <c r="D25" s="132"/>
+      <c r="E25" s="132"/>
+      <c r="F25" s="133"/>
+      <c r="G25" s="125"/>
+      <c r="H25" s="125"/>
+      <c r="I25" s="108"/>
+      <c r="J25" s="109"/>
+      <c r="K25" s="109"/>
+      <c r="L25" s="109"/>
+      <c r="M25" s="109"/>
+      <c r="N25" s="109"/>
+      <c r="O25" s="109"/>
+      <c r="P25" s="109"/>
+      <c r="Q25" s="110"/>
       <c r="R25" s="7"/>
       <c r="S25" s="7"/>
       <c r="T25" s="7"/>
@@ -15148,48 +15148,48 @@
     </row>
     <row r="26" spans="1:32" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A26" s="7"/>
-      <c r="B26" s="158" t="s">
+      <c r="B26" s="126" t="s">
         <v>11</v>
       </c>
-      <c r="C26" s="158" t="s">
+      <c r="C26" s="126" t="s">
         <v>12</v>
       </c>
-      <c r="D26" s="142" t="s">
+      <c r="D26" s="134" t="s">
         <v>49</v>
       </c>
-      <c r="E26" s="142" t="s">
+      <c r="E26" s="134" t="s">
         <v>50</v>
       </c>
-      <c r="F26" s="144" t="s">
+      <c r="F26" s="136" t="s">
         <v>68</v>
       </c>
-      <c r="G26" s="155"/>
-      <c r="H26" s="155"/>
-      <c r="I26" s="169" t="s">
+      <c r="G26" s="125"/>
+      <c r="H26" s="125"/>
+      <c r="I26" s="114" t="s">
         <v>55</v>
       </c>
-      <c r="J26" s="169" t="s">
+      <c r="J26" s="114" t="s">
         <v>56</v>
       </c>
-      <c r="K26" s="156" t="s">
+      <c r="K26" s="103" t="s">
         <v>76</v>
       </c>
-      <c r="L26" s="156" t="s">
+      <c r="L26" s="103" t="s">
         <v>54</v>
       </c>
-      <c r="M26" s="156" t="s">
+      <c r="M26" s="103" t="s">
         <v>61</v>
       </c>
-      <c r="N26" s="156" t="s">
+      <c r="N26" s="103" t="s">
         <v>64</v>
       </c>
-      <c r="O26" s="156" t="s">
+      <c r="O26" s="103" t="s">
         <v>75</v>
       </c>
-      <c r="P26" s="156" t="s">
+      <c r="P26" s="103" t="s">
         <v>66</v>
       </c>
-      <c r="Q26" s="156" t="s">
+      <c r="Q26" s="103" t="s">
         <v>67</v>
       </c>
       <c r="R26" s="9"/>
@@ -15210,22 +15210,22 @@
     </row>
     <row r="27" spans="1:32" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A27" s="7"/>
-      <c r="B27" s="159"/>
-      <c r="C27" s="159"/>
-      <c r="D27" s="143"/>
-      <c r="E27" s="143"/>
-      <c r="F27" s="145"/>
-      <c r="G27" s="155"/>
-      <c r="H27" s="155"/>
-      <c r="I27" s="170"/>
-      <c r="J27" s="170"/>
-      <c r="K27" s="157"/>
-      <c r="L27" s="157"/>
-      <c r="M27" s="157"/>
-      <c r="N27" s="157"/>
-      <c r="O27" s="157"/>
-      <c r="P27" s="157"/>
-      <c r="Q27" s="157"/>
+      <c r="B27" s="127"/>
+      <c r="C27" s="127"/>
+      <c r="D27" s="135"/>
+      <c r="E27" s="135"/>
+      <c r="F27" s="137"/>
+      <c r="G27" s="125"/>
+      <c r="H27" s="125"/>
+      <c r="I27" s="115"/>
+      <c r="J27" s="115"/>
+      <c r="K27" s="104"/>
+      <c r="L27" s="104"/>
+      <c r="M27" s="104"/>
+      <c r="N27" s="104"/>
+      <c r="O27" s="104"/>
+      <c r="P27" s="104"/>
+      <c r="Q27" s="104"/>
       <c r="R27" s="7"/>
       <c r="S27" s="7"/>
       <c r="T27" s="7"/>
@@ -15251,31 +15251,31 @@
         <v>80</v>
       </c>
       <c r="D28" s="48">
-        <v>0.97789599999999988</v>
+        <v>-0.1223633442417989</v>
       </c>
       <c r="E28" s="48">
-        <v>1.067612</v>
+        <v>-0.65153095448481257</v>
       </c>
       <c r="F28" s="58">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="G28" s="155"/>
-      <c r="H28" s="155"/>
+      <c r="G28" s="125"/>
+      <c r="H28" s="125"/>
       <c r="I28" s="55">
         <f t="shared" ref="I28:I47" si="1">IF(D28=0,"",LOG($K$15*10^D28+$K$16*10^E28+$K$14))</f>
-        <v>1.9910902187249287E-2</v>
+        <v>-6.2092895899633685E-4</v>
       </c>
       <c r="J28" s="55">
         <f t="shared" ref="J28:J47" si="2">IF(D28=0,"",LOG($K$21*10^D28+$K$22*10^E28+$K$20))</f>
-        <v>0.30848772388839846</v>
+        <v>-1.7911449240931149E-2</v>
       </c>
       <c r="K28" s="56">
         <f t="shared" ref="K28:K47" si="3">IF(D28=0,"",1/(1+10^D28*$J$15/$J$14+10^E28*$J$16/$J$14+10^J28*$J$19/$J$14))</f>
-        <v>0.94995769256555962</v>
+        <v>0.99594669571161965</v>
       </c>
       <c r="L28" s="56">
         <f t="shared" ref="L28:L47" si="4">IF(D28=0,"",1/(1+10^I28/10^J28*$J$13/$J$19))</f>
-        <v>2.5353776371013245E-38</v>
+        <v>1.2536471375943667E-38</v>
       </c>
       <c r="M28" s="56">
         <f t="shared" ref="M28:M47" si="5">IF(D28=0,"",1-L28)</f>
@@ -15283,23 +15283,23 @@
       </c>
       <c r="N28" s="56">
         <f t="shared" ref="N28:N47" si="6">IF(D28=0,"",1/(1/10^E28*$J$20/$J$22+10^D28/10^E28*$J$21/$J$22+10^I28/10^E28*$J$13/$J$22+1))</f>
-        <v>3.2729853028573287E-39</v>
+        <v>6.5513821305467143E-41</v>
       </c>
       <c r="O28" s="57">
         <f t="shared" ref="O28:O47" si="7">IF(D28=0,"",F28*K28*$J$7/$J$14)</f>
-        <v>9.5518852790615213E-6</v>
+        <v>1.0014307643328285E-5</v>
       </c>
       <c r="P28" s="57">
         <f t="shared" ref="P28:P47" si="8">IF(D28=0,"",O28*10^J28)</f>
-        <v>1.9434654381188461E-5</v>
+        <v>9.6096922519866151E-6</v>
       </c>
       <c r="Q28" s="57">
         <f t="shared" ref="Q28:Q47" si="9">IF(D28=0,"",F28*N28*$J$7/$J$22)</f>
-        <v>1.1160948336559955E-4</v>
+        <v>2.2340350085978156E-6</v>
       </c>
       <c r="R28" s="9">
         <f>O28/F28</f>
-        <v>0.95518852790615205</v>
+        <v>1.0014307643328284</v>
       </c>
       <c r="S28" s="11"/>
       <c r="T28" s="7"/>
@@ -15333,8 +15333,8 @@
       <c r="F29" s="58">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="G29" s="155"/>
-      <c r="H29" s="155"/>
+      <c r="G29" s="125"/>
+      <c r="H29" s="125"/>
       <c r="I29" s="55">
         <f t="shared" si="1"/>
         <v>0.13647749932435757</v>
@@ -15372,7 +15372,7 @@
         <v>8.7674137197416642E-4</v>
       </c>
       <c r="R29" s="9">
-        <f t="shared" ref="R29:R54" si="10">O29/F29</f>
+        <f t="shared" ref="R29:R57" si="10">O29/F29</f>
         <v>0.73033565037896497</v>
       </c>
       <c r="S29" s="7"/>
@@ -15398,50 +15398,57 @@
       <c r="C30" s="47" t="s">
         <v>84</v>
       </c>
-      <c r="D30" s="48"/>
-      <c r="E30" s="48"/>
+      <c r="D30" s="48">
+        <v>2.848199987724402</v>
+      </c>
+      <c r="E30" s="48">
+        <v>3.5741999825375301</v>
+      </c>
       <c r="F30" s="58">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="G30" s="155"/>
-      <c r="H30" s="155"/>
-      <c r="I30" s="55" t="str">
+      <c r="G30" s="125"/>
+      <c r="H30" s="125"/>
+      <c r="I30" s="55">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J30" s="55" t="str">
+        <v>0.72733479513716004</v>
+      </c>
+      <c r="J30" s="55">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K30" s="86" t="str">
+        <v>2.1792047088105391</v>
+      </c>
+      <c r="K30" s="86">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="L30" s="56" t="str">
+        <v>0.18632896473248875</v>
+      </c>
+      <c r="L30" s="56">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="M30" s="56" t="str">
+        <v>3.69262960592219E-37</v>
+      </c>
+      <c r="M30" s="56">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="N30" s="56" t="str">
+        <v>1</v>
+      </c>
+      <c r="N30" s="56">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="O30" s="57" t="str">
+        <v>2.0611430996366476E-37</v>
+      </c>
+      <c r="O30" s="57">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="P30" s="57" t="str">
+        <v>1.8735496424944248E-6</v>
+      </c>
+      <c r="P30" s="57">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="Q30" s="57" t="str">
+        <v>2.8305440222660557E-4</v>
+      </c>
+      <c r="Q30" s="57">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="R30" s="9"/>
+        <v>7.0285410781462474E-3</v>
+      </c>
+      <c r="R30" s="9">
+        <f t="shared" si="10"/>
+        <v>0.18735496424944245</v>
+      </c>
       <c r="S30" s="7"/>
       <c r="T30" s="7"/>
       <c r="U30" s="7"/>
@@ -15465,50 +15472,57 @@
       <c r="C31" s="47" t="s">
         <v>86</v>
       </c>
-      <c r="D31" s="48"/>
-      <c r="E31" s="48"/>
+      <c r="D31" s="48">
+        <v>-0.98996462433878363</v>
+      </c>
+      <c r="E31" s="48">
+        <v>-1.885724324763622</v>
+      </c>
       <c r="F31" s="58">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="G31" s="155"/>
-      <c r="H31" s="155"/>
-      <c r="I31" s="55" t="str">
+      <c r="G31" s="125"/>
+      <c r="H31" s="125"/>
+      <c r="I31" s="55">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J31" s="55" t="str">
+        <v>-2.1463428094334056E-3</v>
+      </c>
+      <c r="J31" s="55">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K31" s="56" t="str">
+        <v>-4.8686976382071145E-2</v>
+      </c>
+      <c r="K31" s="56">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="L31" s="56" t="str">
+        <v>0.99945100475420556</v>
+      </c>
+      <c r="L31" s="56">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="M31" s="56" t="str">
+        <v>1.1719934920763741E-38</v>
+      </c>
+      <c r="M31" s="56">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="N31" s="56" t="str">
+        <v>1</v>
+      </c>
+      <c r="N31" s="56">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="O31" s="57" t="str">
+        <v>3.8341135914917693E-42</v>
+      </c>
+      <c r="O31" s="57">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="P31" s="57" t="str">
+        <v>1.0049543694595745E-5</v>
+      </c>
+      <c r="P31" s="57">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="Q31" s="57" t="str">
+        <v>8.9837853431363123E-6</v>
+      </c>
+      <c r="Q31" s="57">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="R31" s="9"/>
+        <v>1.307440753668649E-7</v>
+      </c>
+      <c r="R31" s="9">
+        <f t="shared" si="10"/>
+        <v>1.0049543694595744</v>
+      </c>
       <c r="S31" s="7"/>
       <c r="T31" s="7"/>
       <c r="U31" s="7"/>
@@ -15541,8 +15555,8 @@
       <c r="F32" s="58">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="G32" s="155"/>
-      <c r="H32" s="155"/>
+      <c r="G32" s="125"/>
+      <c r="H32" s="125"/>
       <c r="I32" s="55">
         <f t="shared" si="1"/>
         <v>1.205792825575362</v>
@@ -15606,50 +15620,57 @@
       <c r="C33" s="47" t="s">
         <v>90</v>
       </c>
-      <c r="D33" s="48"/>
-      <c r="E33" s="48"/>
+      <c r="D33" s="48">
+        <v>-7.2373500000194575</v>
+      </c>
+      <c r="E33" s="48">
+        <v>-10.772850000027681</v>
+      </c>
       <c r="F33" s="58">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="G33" s="155"/>
-      <c r="H33" s="155"/>
-      <c r="I33" s="55" t="str">
+      <c r="G33" s="125"/>
+      <c r="H33" s="125"/>
+      <c r="I33" s="55">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J33" s="55" t="str">
+        <v>-2.38483375204565E-3</v>
+      </c>
+      <c r="J33" s="55">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K33" s="56" t="str">
+        <v>-5.3500443514237071E-2</v>
+      </c>
+      <c r="K33" s="56">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="L33" s="56" t="str">
+        <v>0.99999999969041098</v>
+      </c>
+      <c r="L33" s="56">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="M33" s="56" t="str">
+        <v>1.1597121947133718E-38</v>
+      </c>
+      <c r="M33" s="56">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="N33" s="56" t="str">
+        <v>1</v>
+      </c>
+      <c r="N33" s="56">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="O33" s="57" t="str">
+        <v>4.9748248044425739E-51</v>
+      </c>
+      <c r="O33" s="57">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="P33" s="57" t="str">
+        <v>1.0055063873747364E-5</v>
+      </c>
+      <c r="P33" s="57">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="Q33" s="57" t="str">
+        <v>8.8896444285404792E-6</v>
+      </c>
+      <c r="Q33" s="57">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="R33" s="9"/>
+        <v>1.6964256630589845E-16</v>
+      </c>
+      <c r="R33" s="9">
+        <f t="shared" si="10"/>
+        <v>1.0055063873747363</v>
+      </c>
       <c r="S33" s="7"/>
       <c r="T33" s="7"/>
       <c r="U33" s="7"/>
@@ -15673,50 +15694,57 @@
       <c r="C34" s="47" t="s">
         <v>92</v>
       </c>
-      <c r="D34" s="48"/>
-      <c r="E34" s="48"/>
+      <c r="D34" s="48">
+        <v>0.89837073464087869</v>
+      </c>
+      <c r="E34" s="48">
+        <v>0.80049921406660218</v>
+      </c>
       <c r="F34" s="58">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="G34" s="155"/>
-      <c r="H34" s="155"/>
-      <c r="I34" s="55" t="str">
+      <c r="G34" s="125"/>
+      <c r="H34" s="125"/>
+      <c r="I34" s="55">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J34" s="55" t="str">
+        <v>1.6033091379554689E-2</v>
+      </c>
+      <c r="J34" s="55">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K34" s="56" t="str">
+        <v>0.24684621561358433</v>
+      </c>
+      <c r="K34" s="56">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="L34" s="56" t="str">
+        <v>0.95847783622330018</v>
+      </c>
+      <c r="L34" s="56">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="M34" s="56" t="str">
+        <v>2.2196216790399494E-38</v>
+      </c>
+      <c r="M34" s="56">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="N34" s="56" t="str">
+        <v>1</v>
+      </c>
+      <c r="N34" s="56">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="O34" s="57" t="str">
+        <v>1.7852912646800246E-39</v>
+      </c>
+      <c r="O34" s="57">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="P34" s="57" t="str">
+        <v>9.6375558677801308E-6</v>
+      </c>
+      <c r="P34" s="57">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="Q34" s="57" t="str">
+        <v>1.7014262316541322E-5</v>
+      </c>
+      <c r="Q34" s="57">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="R34" s="9"/>
+        <v>6.0878805515596E-5</v>
+      </c>
+      <c r="R34" s="9">
+        <f t="shared" si="10"/>
+        <v>0.96375558677801298</v>
+      </c>
       <c r="S34" s="7"/>
       <c r="T34" s="7"/>
       <c r="U34" s="7"/>
@@ -15740,50 +15768,57 @@
       <c r="C35" s="47" t="s">
         <v>94</v>
       </c>
-      <c r="D35" s="48"/>
-      <c r="E35" s="48"/>
+      <c r="D35" s="48">
+        <v>5.1201999877244022</v>
+      </c>
+      <c r="E35" s="48">
+        <v>6.8061999825375299</v>
+      </c>
       <c r="F35" s="58">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="G35" s="155"/>
-      <c r="H35" s="155"/>
-      <c r="I35" s="55" t="str">
+      <c r="G35" s="125"/>
+      <c r="H35" s="125"/>
+      <c r="I35" s="55">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J35" s="55" t="str">
+        <v>3.2343164583424695</v>
+      </c>
+      <c r="J35" s="55">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K35" s="56" t="str">
+        <v>5.1936660384397202</v>
+      </c>
+      <c r="K35" s="56">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="L35" s="56" t="str">
+        <v>5.7982736460576007E-4</v>
+      </c>
+      <c r="L35" s="56">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="M35" s="56" t="str">
+        <v>1.1879971910413874E-36</v>
+      </c>
+      <c r="M35" s="56">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="N35" s="56" t="str">
+        <v>1</v>
+      </c>
+      <c r="N35" s="56">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="O35" s="57" t="str">
+        <v>1.0942750104682087E-36</v>
+      </c>
+      <c r="O35" s="57">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="P35" s="57" t="str">
+        <v>5.8302011886624859E-9</v>
+      </c>
+      <c r="P35" s="57">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="Q35" s="57" t="str">
+        <v>9.1064599118688937E-4</v>
+      </c>
+      <c r="Q35" s="57">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="R35" s="9"/>
+        <v>3.7315006722340477E-2</v>
+      </c>
+      <c r="R35" s="9">
+        <f t="shared" si="10"/>
+        <v>5.8302011886624851E-4</v>
+      </c>
       <c r="S35" s="7"/>
       <c r="T35" s="7"/>
       <c r="U35" s="7"/>
@@ -15816,8 +15851,8 @@
       <c r="F36" s="58">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="G36" s="155"/>
-      <c r="H36" s="155"/>
+      <c r="G36" s="125"/>
+      <c r="H36" s="125"/>
       <c r="I36" s="55">
         <f t="shared" si="1"/>
         <v>9.4490273200873776E-2</v>
@@ -15890,8 +15925,8 @@
       <c r="F37" s="58">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="G37" s="155"/>
-      <c r="H37" s="155"/>
+      <c r="G37" s="125"/>
+      <c r="H37" s="125"/>
       <c r="I37" s="55">
         <f t="shared" si="1"/>
         <v>0.18219557821644855</v>
@@ -15964,8 +15999,8 @@
       <c r="F38" s="58">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="G38" s="155"/>
-      <c r="H38" s="155"/>
+      <c r="G38" s="125"/>
+      <c r="H38" s="125"/>
       <c r="I38" s="55">
         <f t="shared" si="1"/>
         <v>6.3870952141755781E-3</v>
@@ -16029,50 +16064,57 @@
       <c r="C39" s="47" t="s">
         <v>102</v>
       </c>
-      <c r="D39" s="48"/>
-      <c r="E39" s="48"/>
+      <c r="D39" s="48">
+        <v>4.3320999877244022</v>
+      </c>
+      <c r="E39" s="48">
+        <v>5.6850999825375297</v>
+      </c>
       <c r="F39" s="58">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="G39" s="155"/>
-      <c r="H39" s="155"/>
-      <c r="I39" s="55" t="str">
+      <c r="G39" s="125"/>
+      <c r="H39" s="125"/>
+      <c r="I39" s="55">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J39" s="55" t="str">
+        <v>2.2830290403350468</v>
+      </c>
+      <c r="J39" s="55">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K39" s="56" t="str">
+        <v>4.1103934248091365</v>
+      </c>
+      <c r="K39" s="56">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="L39" s="56" t="str">
+        <v>5.183058680549182E-3</v>
+      </c>
+      <c r="L39" s="56">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="M39" s="56" t="str">
+        <v>8.7665803595652168E-37</v>
+      </c>
+      <c r="M39" s="56">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="N39" s="56" t="str">
+        <v>1</v>
+      </c>
+      <c r="N39" s="56">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="O39" s="57" t="str">
+        <v>7.4014004047284845E-37</v>
+      </c>
+      <c r="O39" s="57">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="P39" s="57" t="str">
+        <v>5.2115986110437298E-8</v>
+      </c>
+      <c r="P39" s="57">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="Q39" s="57" t="str">
+        <v>6.7199243576137918E-4</v>
+      </c>
+      <c r="Q39" s="57">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="R39" s="9"/>
+        <v>2.5238930178895894E-2</v>
+      </c>
+      <c r="R39" s="9">
+        <f t="shared" si="10"/>
+        <v>5.2115986110437291E-3</v>
+      </c>
       <c r="S39" s="7"/>
       <c r="T39" s="7"/>
       <c r="U39" s="7"/>
@@ -16096,50 +16138,57 @@
       <c r="C40" s="47" t="s">
         <v>104</v>
       </c>
-      <c r="D40" s="48"/>
-      <c r="E40" s="48"/>
+      <c r="D40" s="48">
+        <v>2.713299987724402</v>
+      </c>
+      <c r="E40" s="48">
+        <v>3.3822999825375302</v>
+      </c>
       <c r="F40" s="58">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="G40" s="155"/>
-      <c r="H40" s="155"/>
-      <c r="I40" s="55" t="str">
+      <c r="G40" s="125"/>
+      <c r="H40" s="125"/>
+      <c r="I40" s="55">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J40" s="55" t="str">
+        <v>0.61535497616766821</v>
+      </c>
+      <c r="J40" s="55">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K40" s="56" t="str">
+        <v>2.0144079910299482</v>
+      </c>
+      <c r="K40" s="56">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="L40" s="56" t="str">
+        <v>0.24113496584831146</v>
+      </c>
+      <c r="L40" s="56">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="M40" s="56" t="str">
+        <v>3.2697823750520026E-37</v>
+      </c>
+      <c r="M40" s="56">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="N40" s="56" t="str">
+        <v>1</v>
+      </c>
+      <c r="N40" s="56">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="O40" s="57" t="str">
+        <v>1.7146992729043089E-37</v>
+      </c>
+      <c r="O40" s="57">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="P40" s="57" t="str">
+        <v>2.424627484549299E-6</v>
+      </c>
+      <c r="P40" s="57">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="Q40" s="57" t="str">
+        <v>2.5064151955481488E-4</v>
+      </c>
+      <c r="Q40" s="57">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="R40" s="9"/>
+        <v>5.8471603831873765E-3</v>
+      </c>
+      <c r="R40" s="9">
+        <f t="shared" si="10"/>
+        <v>0.24246274845492988</v>
+      </c>
       <c r="S40" s="7"/>
       <c r="T40" s="7"/>
       <c r="U40" s="7"/>
@@ -16172,8 +16221,8 @@
       <c r="F41" s="58">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="G41" s="155"/>
-      <c r="H41" s="155"/>
+      <c r="G41" s="125"/>
+      <c r="H41" s="125"/>
       <c r="I41" s="55">
         <f t="shared" si="1"/>
         <v>1.4041054944130613</v>
@@ -16238,31 +16287,31 @@
         <v>108</v>
       </c>
       <c r="D42" s="48">
-        <v>2.0168880000000002</v>
+        <v>-1.2627122753537208</v>
       </c>
       <c r="E42" s="48">
-        <v>2.2161360000000005</v>
+        <v>-2.2737174621228986</v>
       </c>
       <c r="F42" s="58">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="G42" s="155"/>
-      <c r="H42" s="155"/>
+      <c r="G42" s="125"/>
+      <c r="H42" s="125"/>
       <c r="I42" s="55">
         <f t="shared" si="1"/>
-        <v>0.19684998721960828</v>
+        <v>-2.2576598370427073E-3</v>
       </c>
       <c r="J42" s="55">
         <f t="shared" si="2"/>
-        <v>1.1551707744460811</v>
+        <v>-5.0942888713472134E-2</v>
       </c>
       <c r="K42" s="56">
         <f t="shared" si="3"/>
-        <v>0.6320700015111097</v>
+        <v>0.99970721379975491</v>
       </c>
       <c r="L42" s="56">
         <f t="shared" si="4"/>
-        <v>1.1851862951957214E-37</v>
+        <v>1.166220321585951E-38</v>
       </c>
       <c r="M42" s="56">
         <f t="shared" si="5"/>
@@ -16270,23 +16319,23 @@
       </c>
       <c r="N42" s="56">
         <f t="shared" si="6"/>
-        <v>3.0656951732852954E-38</v>
+        <v>1.5695789116662759E-42</v>
       </c>
       <c r="O42" s="57">
         <f t="shared" si="7"/>
-        <v>6.3555042398413953E-6</v>
+        <v>1.0052119892914574E-5</v>
       </c>
       <c r="P42" s="57">
         <f t="shared" si="8"/>
-        <v>9.0849133034021133E-5</v>
+        <v>8.9395317489090943E-6</v>
       </c>
       <c r="Q42" s="57">
         <f t="shared" si="9"/>
-        <v>1.0454084659288767E-3</v>
+        <v>5.3522969162030867E-8</v>
       </c>
       <c r="R42" s="9">
         <f t="shared" si="10"/>
-        <v>0.63555042398413952</v>
+        <v>1.0052119892914573</v>
       </c>
       <c r="S42" s="7"/>
       <c r="T42" s="7"/>
@@ -16312,31 +16361,31 @@
         <v>110</v>
       </c>
       <c r="D43" s="48">
-        <v>4.2132720000000008</v>
+        <v>2.1582748772295566</v>
       </c>
       <c r="E43" s="48">
-        <v>4.705258999999999</v>
+        <v>2.5927572197209185</v>
       </c>
       <c r="F43" s="58">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="G43" s="155"/>
-      <c r="H43" s="155"/>
+      <c r="G43" s="125"/>
+      <c r="H43" s="125"/>
       <c r="I43" s="55">
         <f t="shared" si="1"/>
-        <v>1.9819193824026036</v>
+        <v>0.26057631865908987</v>
       </c>
       <c r="J43" s="55">
         <f t="shared" si="2"/>
-        <v>3.4261628681049148</v>
+        <v>1.3642805972747696</v>
       </c>
       <c r="K43" s="56">
         <f t="shared" si="3"/>
-        <v>1.0368018983614901E-2</v>
+        <v>0.54580668108038899</v>
       </c>
       <c r="L43" s="56">
         <f t="shared" si="4"/>
-        <v>3.6283512181793172E-37</v>
+        <v>1.6564186523571383E-37</v>
       </c>
       <c r="M43" s="56">
         <f t="shared" si="5"/>
@@ -16344,23 +16393,23 @@
       </c>
       <c r="N43" s="56">
         <f t="shared" si="6"/>
-        <v>1.5508956395281649E-37</v>
+        <v>6.301208619159645E-38</v>
       </c>
       <c r="O43" s="57">
         <f t="shared" si="7"/>
-        <v>1.0425109315674806E-7</v>
+        <v>5.4881210426804299E-6</v>
       </c>
       <c r="P43" s="57">
         <f t="shared" si="8"/>
-        <v>2.7812721413563953E-4</v>
+        <v>1.2697092357381396E-4</v>
       </c>
       <c r="Q43" s="57">
         <f t="shared" si="9"/>
-        <v>5.2885865674553219E-3</v>
+        <v>2.1487253179820554E-3</v>
       </c>
       <c r="R43" s="9">
         <f t="shared" si="10"/>
-        <v>1.0425109315674804E-2</v>
+        <v>0.54881210426804294</v>
       </c>
       <c r="S43" s="7"/>
       <c r="T43" s="7"/>
@@ -16385,50 +16434,57 @@
       <c r="C44" s="47" t="s">
         <v>112</v>
       </c>
-      <c r="D44" s="48"/>
-      <c r="E44" s="48"/>
+      <c r="D44" s="48">
+        <v>0.51229998772440222</v>
+      </c>
+      <c r="E44" s="48">
+        <v>0.25129998253752994</v>
+      </c>
       <c r="F44" s="58">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="G44" s="155"/>
-      <c r="H44" s="155"/>
-      <c r="I44" s="55" t="str">
+      <c r="G44" s="125"/>
+      <c r="H44" s="125"/>
+      <c r="I44" s="55">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J44" s="55" t="str">
+        <v>5.2260244794124344E-3</v>
+      </c>
+      <c r="J44" s="55">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K44" s="56" t="str">
+        <v>8.9237920997135206E-2</v>
+      </c>
+      <c r="K44" s="56">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="L44" s="56" t="str">
+        <v>0.98262801455071158</v>
+      </c>
+      <c r="L44" s="56">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="M44" s="56" t="str">
+        <v>1.5829883919722483E-38</v>
+      </c>
+      <c r="M44" s="56">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="N44" s="56" t="str">
+        <v>1</v>
+      </c>
+      <c r="N44" s="56">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="O44" s="57" t="str">
+        <v>5.1679334855023364E-40</v>
+      </c>
+      <c r="O44" s="57">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="P44" s="57" t="str">
+        <v>9.8803874534998176E-6</v>
+      </c>
+      <c r="P44" s="57">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="Q44" s="57" t="str">
+        <v>1.2134220889708206E-5</v>
+      </c>
+      <c r="Q44" s="57">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="R44" s="9"/>
+        <v>1.7622761271832097E-5</v>
+      </c>
+      <c r="R44" s="9">
+        <f t="shared" si="10"/>
+        <v>0.98803874534998171</v>
+      </c>
       <c r="S44" s="7"/>
       <c r="T44" s="7"/>
       <c r="U44" s="7"/>
@@ -16452,50 +16508,57 @@
       <c r="C45" s="47" t="s">
         <v>114</v>
       </c>
-      <c r="D45" s="48"/>
-      <c r="E45" s="48"/>
+      <c r="D45" s="48">
+        <v>0.92271245461153151</v>
+      </c>
+      <c r="E45" s="48">
+        <v>0.83512616782767168</v>
+      </c>
       <c r="F45" s="58">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="G45" s="155"/>
-      <c r="H45" s="155"/>
-      <c r="I45" s="55" t="str">
+      <c r="G45" s="125"/>
+      <c r="H45" s="125"/>
+      <c r="I45" s="55">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J45" s="55" t="str">
+        <v>1.7082011278319043E-2</v>
+      </c>
+      <c r="J45" s="55">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K45" s="56" t="str">
+        <v>0.26002821205679144</v>
+      </c>
+      <c r="K45" s="56">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="L45" s="56" t="str">
+        <v>0.95616568767124643</v>
+      </c>
+      <c r="L45" s="56">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="M45" s="56" t="str">
+        <v>2.2825065603970897E-38</v>
+      </c>
+      <c r="M45" s="56">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="N45" s="56" t="str">
+        <v>1</v>
+      </c>
+      <c r="N45" s="56">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="O45" s="57" t="str">
+        <v>1.9287996291863749E-39</v>
+      </c>
+      <c r="O45" s="57">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="P45" s="57" t="str">
+        <v>9.614307066396439E-6</v>
+      </c>
+      <c r="P45" s="57">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="Q45" s="57" t="str">
+        <v>1.7496299357924754E-5</v>
+      </c>
+      <c r="Q45" s="57">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="R45" s="9"/>
+        <v>6.5772470759742704E-5</v>
+      </c>
+      <c r="R45" s="9">
+        <f t="shared" si="10"/>
+        <v>0.96143070663964381</v>
+      </c>
       <c r="S45" s="7"/>
       <c r="T45" s="7"/>
       <c r="U45" s="7"/>
@@ -16520,31 +16583,31 @@
         <v>116</v>
       </c>
       <c r="D46" s="48">
-        <v>2.9091840000000002</v>
+        <v>1.6452318246143236</v>
       </c>
       <c r="E46" s="48">
-        <v>3.4102429999999995</v>
+        <v>1.8629354124795308</v>
       </c>
       <c r="F46" s="58">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="G46" s="155"/>
-      <c r="H46" s="155"/>
+      <c r="G46" s="125"/>
+      <c r="H46" s="125"/>
       <c r="I46" s="55">
         <f t="shared" si="1"/>
-        <v>0.75709377136721445</v>
+        <v>9.3777909413029201E-2</v>
       </c>
       <c r="J46" s="55">
         <f t="shared" si="2"/>
-        <v>2.1286974379361929</v>
+        <v>0.82289760622407571</v>
       </c>
       <c r="K46" s="56">
         <f t="shared" si="3"/>
-        <v>0.17398884084392571</v>
+        <v>0.80137770661001506</v>
       </c>
       <c r="L46" s="56">
         <f t="shared" si="4"/>
-        <v>3.0695131640229652E-37</v>
+        <v>6.9917441947984675E-38</v>
       </c>
       <c r="M46" s="56">
         <f t="shared" si="5"/>
@@ -16552,23 +16615,23 @@
       </c>
       <c r="N46" s="56">
         <f t="shared" si="6"/>
-        <v>1.3194477168268915E-37</v>
+        <v>1.7234570321348053E-38</v>
       </c>
       <c r="O46" s="57">
         <f t="shared" si="7"/>
-        <v>1.7494689085465535E-6</v>
+        <v>8.0579040294555153E-6</v>
       </c>
       <c r="P46" s="57">
         <f t="shared" si="8"/>
-        <v>2.3529010664264413E-4</v>
+        <v>5.3594434990340076E-5</v>
       </c>
       <c r="Q46" s="57">
         <f t="shared" si="9"/>
-        <v>4.4993443103581374E-3</v>
+        <v>5.8770245253301069E-4</v>
       </c>
       <c r="R46" s="9">
         <f t="shared" si="10"/>
-        <v>0.17494689085465534</v>
+        <v>0.80579040294555149</v>
       </c>
       <c r="S46" s="7"/>
       <c r="T46" s="7"/>
@@ -16594,31 +16657,31 @@
         <v>118</v>
       </c>
       <c r="D47" s="48">
-        <v>2.7542720000000003</v>
+        <v>2.8951366557581992</v>
       </c>
       <c r="E47" s="48">
-        <v>3.4524839999999992</v>
+        <v>3.6409690455151855</v>
       </c>
       <c r="F47" s="58">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="G47" s="155"/>
-      <c r="H47" s="155"/>
+      <c r="G47" s="125"/>
+      <c r="H47" s="125"/>
       <c r="I47" s="55">
         <f t="shared" si="1"/>
-        <v>0.64964375746132819</v>
+        <v>0.76819655741897375</v>
       </c>
       <c r="J47" s="55">
         <f t="shared" si="2"/>
-        <v>2.0706209788057328</v>
+        <v>2.2370690409846548</v>
       </c>
       <c r="K47" s="56">
         <f t="shared" si="3"/>
-        <v>0.22282884472745612</v>
+        <v>0.16959717297231178</v>
       </c>
       <c r="L47" s="56">
         <f t="shared" si="4"/>
-        <v>3.4390861490399233E-37</v>
+        <v>3.8400627152392865E-37</v>
       </c>
       <c r="M47" s="56">
         <f t="shared" si="5"/>
@@ -16626,23 +16689,23 @@
       </c>
       <c r="N47" s="56">
         <f t="shared" si="6"/>
-        <v>1.8624438997488186E-37</v>
+        <v>2.1878394317628946E-37</v>
       </c>
       <c r="O47" s="57">
         <f t="shared" si="7"/>
-        <v>2.2405582673415568E-6</v>
+        <v>1.7053104075715202E-6</v>
       </c>
       <c r="P47" s="57">
         <f t="shared" si="8"/>
-        <v>2.636193114416595E-4</v>
+        <v>2.9435572271627278E-4</v>
       </c>
       <c r="Q47" s="57">
         <f t="shared" si="9"/>
-        <v>6.3509726507757292E-3</v>
+        <v>7.4605782205245559E-3</v>
       </c>
       <c r="R47" s="9">
         <f t="shared" si="10"/>
-        <v>0.22405582673415567</v>
+        <v>0.170531040757152</v>
       </c>
       <c r="S47" s="7"/>
       <c r="T47" s="7"/>
@@ -16667,50 +16730,57 @@
       <c r="C48" s="47" t="s">
         <v>120</v>
       </c>
-      <c r="D48" s="48"/>
-      <c r="E48" s="48"/>
+      <c r="D48" s="48">
+        <v>-1.7616394390778063</v>
+      </c>
+      <c r="E48" s="48">
+        <v>-2.9834589203782875</v>
+      </c>
       <c r="F48" s="58">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="G48" s="155"/>
-      <c r="H48" s="155"/>
-      <c r="I48" s="83" t="str">
+      <c r="G48" s="125"/>
+      <c r="H48" s="125"/>
+      <c r="I48" s="83">
         <f t="shared" ref="I48:I50" si="11">IF(D48=0,"",LOG($K$15*10^D48+$K$16*10^E48+$K$14))</f>
-        <v/>
-      </c>
-      <c r="J48" s="83" t="str">
+        <v>-2.3445592739619139E-3</v>
+      </c>
+      <c r="J48" s="83">
         <f t="shared" ref="J48:J50" si="12">IF(D48=0,"",LOG($K$21*10^D48+$K$22*10^E48+$K$20))</f>
-        <v/>
-      </c>
-      <c r="K48" s="84" t="str">
+        <v>-5.2695197824890877E-2</v>
+      </c>
+      <c r="K48" s="84">
         <f t="shared" ref="K48:K50" si="13">IF(D48=0,"",1/(1+10^D48*$J$15/$J$14+10^E48*$J$16/$J$14+10^J48*$J$19/$J$14))</f>
-        <v/>
-      </c>
-      <c r="L48" s="84" t="str">
+        <v>0.99990726857737144</v>
+      </c>
+      <c r="L48" s="84">
         <f t="shared" ref="L48:L50" si="14">IF(D48=0,"",1/(1+10^I48/10^J48*$J$13/$J$19))</f>
-        <v/>
-      </c>
-      <c r="M48" s="84" t="str">
+        <v>1.1617567249874914E-38</v>
+      </c>
+      <c r="M48" s="84">
         <f t="shared" ref="M48:M92" si="15">IF(D48=0,"",1-L48)</f>
-        <v/>
-      </c>
-      <c r="N48" s="84" t="str">
+        <v>1</v>
+      </c>
+      <c r="N48" s="84">
         <f t="shared" ref="N48:N50" si="16">IF(D48=0,"",1/(1/10^E48*$J$20/$J$22+10^D48/10^E48*$J$21/$J$22+10^I48/10^E48*$J$13/$J$22+1))</f>
-        <v/>
-      </c>
-      <c r="O48" s="85" t="str">
+        <v>3.0628702267738444E-43</v>
+      </c>
+      <c r="O48" s="85">
         <f t="shared" ref="O48:O92" si="17">IF(D48=0,"",F48*K48*$J$7/$J$14)</f>
-        <v/>
-      </c>
-      <c r="P48" s="85" t="str">
+        <v>1.0054131456482378E-5</v>
+      </c>
+      <c r="P48" s="85">
         <f t="shared" ref="P48:P50" si="18">IF(D48=0,"",O48*10^J48)</f>
-        <v/>
-      </c>
-      <c r="Q48" s="85" t="str">
+        <v>8.9053165472292047E-6</v>
+      </c>
+      <c r="Q48" s="85">
         <f t="shared" ref="Q48:Q50" si="19">IF(D48=0,"",F48*N48*$J$7/$J$22)</f>
-        <v/>
-      </c>
-      <c r="R48" s="9"/>
+        <v>1.0444451532601541E-8</v>
+      </c>
+      <c r="R48" s="9">
+        <f t="shared" si="10"/>
+        <v>1.0054131456482378</v>
+      </c>
       <c r="S48" s="7"/>
       <c r="T48" s="7"/>
       <c r="U48" s="7"/>
@@ -16735,31 +16805,31 @@
         <v>122</v>
       </c>
       <c r="D49" s="48">
-        <v>2.3368320000000007</v>
+        <v>1.1365502998865107</v>
       </c>
       <c r="E49" s="48">
-        <v>2.6380540000000012</v>
+        <v>1.1393180322329237</v>
       </c>
       <c r="F49" s="58">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="G49" s="155"/>
-      <c r="H49" s="155"/>
+      <c r="G49" s="125"/>
+      <c r="H49" s="125"/>
       <c r="I49" s="55">
         <f t="shared" si="11"/>
-        <v>0.34601742547413256</v>
+        <v>2.9194031483758934E-2</v>
       </c>
       <c r="J49" s="55">
         <f t="shared" si="12"/>
-        <v>1.4905655210846163</v>
+        <v>0.39328086995694733</v>
       </c>
       <c r="K49" s="56">
         <f t="shared" si="13"/>
-        <v>0.44832993804839766</v>
+        <v>0.92986764082672624</v>
       </c>
       <c r="L49" s="56">
         <f t="shared" si="14"/>
-        <v>1.8197592235054945E-37</v>
+        <v>3.0168427400567719E-38</v>
       </c>
       <c r="M49" s="56">
         <f t="shared" si="15"/>
@@ -16767,23 +16837,23 @@
       </c>
       <c r="N49" s="56">
         <f t="shared" si="16"/>
-        <v>5.7448610884875465E-38</v>
+        <v>3.7789135619754592E-39</v>
       </c>
       <c r="O49" s="57">
         <f t="shared" si="17"/>
-        <v>4.5079861649854602E-6</v>
+        <v>9.3498785255381242E-6</v>
       </c>
       <c r="P49" s="57">
         <f t="shared" si="18"/>
-        <v>1.3949161280070005E-4</v>
+        <v>2.3125271406287858E-5</v>
       </c>
       <c r="Q49" s="57">
         <f t="shared" si="19"/>
-        <v>1.9590096464334179E-3</v>
+        <v>1.2886174281538575E-4</v>
       </c>
       <c r="R49" s="9">
         <f t="shared" si="10"/>
-        <v>0.45079861649854597</v>
+        <v>0.93498785255381234</v>
       </c>
       <c r="S49" s="7"/>
       <c r="T49" s="7"/>
@@ -16809,31 +16879,31 @@
         <v>124</v>
       </c>
       <c r="D50" s="48">
-        <v>9.5872000000000845E-2</v>
+        <v>-0.16497034264114602</v>
       </c>
       <c r="E50" s="48">
-        <v>7.4959000000001108E-2</v>
+        <v>-0.71214090995430623</v>
       </c>
       <c r="F50" s="58">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="G50" s="155"/>
-      <c r="H50" s="155"/>
+      <c r="G50" s="125"/>
+      <c r="H50" s="125"/>
       <c r="I50" s="55">
         <f t="shared" si="11"/>
-        <v>5.8305673796182119E-4</v>
+        <v>-7.8602359813441847E-4</v>
       </c>
       <c r="J50" s="55">
         <f t="shared" si="12"/>
-        <v>1.1702453081905635E-2</v>
+        <v>-2.1200499850457272E-2</v>
       </c>
       <c r="K50" s="56">
         <f t="shared" si="13"/>
-        <v>0.99318947674281288</v>
+        <v>0.99632537129663412</v>
       </c>
       <c r="L50" s="56">
         <f t="shared" si="14"/>
-        <v>1.3383978491401679E-38</v>
+        <v>1.2446617903648383E-38</v>
       </c>
       <c r="M50" s="56">
         <f t="shared" si="15"/>
@@ -16841,23 +16911,23 @@
       </c>
       <c r="N50" s="56">
         <f t="shared" si="16"/>
-        <v>3.4803177830269858E-40</v>
+        <v>5.7001734499215699E-41</v>
       </c>
       <c r="O50" s="57">
         <f t="shared" si="17"/>
-        <v>9.986583630474443E-6</v>
+        <v>1.0018115250524213E-5</v>
       </c>
       <c r="P50" s="57">
         <f t="shared" si="18"/>
-        <v>1.0259339374904194E-5</v>
+        <v>9.5408160753786552E-6</v>
       </c>
       <c r="Q50" s="57">
         <f t="shared" si="19"/>
-        <v>1.1867956430254794E-5</v>
+        <v>1.9437710682191406E-6</v>
       </c>
       <c r="R50" s="9">
         <f t="shared" si="10"/>
-        <v>0.99865836304744426</v>
+        <v>1.0018115250524213</v>
       </c>
       <c r="S50" s="7"/>
       <c r="T50" s="7"/>
@@ -16882,50 +16952,57 @@
       <c r="C51" s="47" t="s">
         <v>126</v>
       </c>
-      <c r="D51" s="48"/>
-      <c r="E51" s="48"/>
+      <c r="D51" s="48">
+        <v>-2.7256879443499291</v>
+      </c>
+      <c r="E51" s="48">
+        <v>-4.3548518644977863</v>
+      </c>
       <c r="F51" s="58">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="G51" s="155"/>
-      <c r="H51" s="155"/>
-      <c r="I51" s="55" t="str">
+      <c r="G51" s="125"/>
+      <c r="H51" s="125"/>
+      <c r="I51" s="55">
         <f t="shared" ref="I51:I70" si="20">IF(D51=0,"",LOG($K$15*10^D51+$K$16*10^E51+$K$14))</f>
-        <v/>
-      </c>
-      <c r="J51" s="55" t="str">
+        <v>-2.3804634030245649E-3</v>
+      </c>
+      <c r="J51" s="55">
         <f t="shared" ref="J51:J70" si="21">IF(D51=0,"",LOG($K$21*10^D51+$K$22*10^E51+$K$20))</f>
-        <v/>
-      </c>
-      <c r="K51" s="56" t="str">
+        <v>-5.341365756501526E-2</v>
+      </c>
+      <c r="K51" s="56">
         <f t="shared" ref="K51:K70" si="22">IF(D51=0,"",1/(1+10^D51*$J$15/$J$14+10^E51*$J$16/$J$14+10^J51*$J$19/$J$14))</f>
-        <v/>
-      </c>
-      <c r="L51" s="56" t="str">
+        <v>0.99998993664053948</v>
+      </c>
+      <c r="L51" s="56">
         <f t="shared" ref="L51:L70" si="23">IF(D51=0,"",1/(1+10^I51/10^J51*$J$13/$J$19))</f>
-        <v/>
-      </c>
-      <c r="M51" s="56" t="str">
+        <v>1.1599322929417573E-38</v>
+      </c>
+      <c r="M51" s="56">
         <f t="shared" ref="M51:M70" si="24">IF(D51=0,"",1-L51)</f>
-        <v/>
-      </c>
-      <c r="N51" s="56" t="str">
+        <v>1</v>
+      </c>
+      <c r="N51" s="56">
         <f t="shared" ref="N51:N70" si="25">IF(D51=0,"",1/(1/10^E51*$J$20/$J$22+10^D51/10^E51*$J$21/$J$22+10^I51/10^E51*$J$13/$J$22+1))</f>
-        <v/>
-      </c>
-      <c r="O51" s="57" t="str">
+        <v>1.3024814783649132E-44</v>
+      </c>
+      <c r="O51" s="57">
         <f t="shared" ref="O51:O70" si="26">IF(D51=0,"",F51*K51*$J$7/$J$14)</f>
-        <v/>
-      </c>
-      <c r="P51" s="57" t="str">
+        <v>1.0054962689138109E-5</v>
+      </c>
+      <c r="P51" s="57">
         <f t="shared" ref="P51:P70" si="27">IF(D51=0,"",O51*10^J51)</f>
-        <v/>
-      </c>
-      <c r="Q51" s="57" t="str">
+        <v>8.8913315669517256E-6</v>
+      </c>
+      <c r="Q51" s="57">
         <f t="shared" ref="Q51:Q70" si="28">IF(D51=0,"",F51*N51*$J$7/$J$22)</f>
-        <v/>
-      </c>
-      <c r="R51" s="9"/>
+        <v>4.4414890823573921E-10</v>
+      </c>
+      <c r="R51" s="9">
+        <f t="shared" si="10"/>
+        <v>1.0054962689138107</v>
+      </c>
       <c r="S51" s="7"/>
       <c r="T51" s="7"/>
       <c r="U51" s="7"/>
@@ -16949,50 +17026,57 @@
       <c r="C52" s="47" t="s">
         <v>128</v>
       </c>
-      <c r="D52" s="48"/>
-      <c r="E52" s="48"/>
+      <c r="D52" s="48">
+        <v>-0.21545001227559774</v>
+      </c>
+      <c r="E52" s="48">
+        <v>-0.78395001746247006</v>
+      </c>
       <c r="F52" s="58">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="G52" s="155"/>
-      <c r="H52" s="155"/>
-      <c r="I52" s="55" t="str">
+      <c r="G52" s="125"/>
+      <c r="H52" s="125"/>
+      <c r="I52" s="55">
         <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="J52" s="55" t="str">
+        <v>-9.6174866178574947E-4</v>
+      </c>
+      <c r="J52" s="55">
         <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="K52" s="56" t="str">
+        <v>-2.4715317794995736E-2</v>
+      </c>
+      <c r="K52" s="56">
         <f t="shared" si="22"/>
-        <v/>
-      </c>
-      <c r="L52" s="56" t="str">
+        <v>0.99672858794301522</v>
+      </c>
+      <c r="L52" s="56">
         <f t="shared" si="23"/>
-        <v/>
-      </c>
-      <c r="M52" s="56" t="str">
+        <v>1.2351288457676123E-38</v>
+      </c>
+      <c r="M52" s="56">
         <f t="shared" si="24"/>
-        <v/>
-      </c>
-      <c r="N52" s="56" t="str">
+        <v>1</v>
+      </c>
+      <c r="N52" s="56">
         <f t="shared" si="25"/>
-        <v/>
-      </c>
-      <c r="O52" s="57" t="str">
+        <v>4.833421710928081E-41</v>
+      </c>
+      <c r="O52" s="57">
         <f t="shared" si="26"/>
-        <v/>
-      </c>
-      <c r="P52" s="57" t="str">
+        <v>1.0022169619659787E-5</v>
+      </c>
+      <c r="P52" s="57">
         <f t="shared" si="27"/>
-        <v/>
-      </c>
-      <c r="Q52" s="57" t="str">
+        <v>9.4677423522492228E-6</v>
+      </c>
+      <c r="Q52" s="57">
         <f t="shared" si="28"/>
-        <v/>
-      </c>
-      <c r="R52" s="9"/>
+        <v>1.6482069124288719E-6</v>
+      </c>
+      <c r="R52" s="9">
+        <f t="shared" si="10"/>
+        <v>1.0022169619659786</v>
+      </c>
       <c r="S52" s="7"/>
       <c r="T52" s="7"/>
       <c r="U52" s="7"/>
@@ -17025,8 +17109,8 @@
       <c r="F53" s="58">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="G53" s="155"/>
-      <c r="H53" s="155"/>
+      <c r="G53" s="125"/>
+      <c r="H53" s="125"/>
       <c r="I53" s="55">
         <f t="shared" si="20"/>
         <v>2.2261664095594637E-2</v>
@@ -17091,31 +17175,31 @@
         <v>132</v>
       </c>
       <c r="D54" s="48">
-        <v>-0.1224400000000001</v>
+        <v>-1.8497486811018407</v>
       </c>
       <c r="E54" s="48">
-        <v>-0.24365499999999995</v>
+        <v>-3.1087974195955765</v>
       </c>
       <c r="F54" s="58">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="G54" s="155"/>
-      <c r="H54" s="155"/>
+      <c r="G54" s="125"/>
+      <c r="H54" s="125"/>
       <c r="I54" s="55">
         <f t="shared" si="20"/>
-        <v>-5.9731855878000166E-4</v>
+        <v>-2.3519591536599349E-3</v>
       </c>
       <c r="J54" s="55">
         <f t="shared" si="21"/>
-        <v>-1.4395700402630798E-2</v>
+        <v>-5.2843716247280528E-2</v>
       </c>
       <c r="K54" s="56">
         <f t="shared" si="22"/>
-        <v>0.99589255258550713</v>
+        <v>0.99992430599516557</v>
       </c>
       <c r="L54" s="56">
         <f t="shared" si="23"/>
-        <v>1.2637682836789922E-38</v>
+        <v>1.1613792880415833E-38</v>
       </c>
       <c r="M54" s="56">
         <f t="shared" si="24"/>
@@ -17123,23 +17207,23 @@
       </c>
       <c r="N54" s="56">
         <f t="shared" si="25"/>
-        <v>1.675657581695649E-40</v>
+        <v>2.2950782479899897E-43</v>
       </c>
       <c r="O54" s="57">
         <f t="shared" si="26"/>
-        <v>1.0013763230736731E-5</v>
+        <v>1.0054302768806595E-5</v>
       </c>
       <c r="P54" s="57">
         <f t="shared" si="27"/>
-        <v>9.6872747679865198E-6</v>
+        <v>8.9024233464345485E-6</v>
       </c>
       <c r="Q54" s="57">
         <f t="shared" si="28"/>
-        <v>5.7140273996168795E-6</v>
+        <v>7.8262648267368019E-9</v>
       </c>
       <c r="R54" s="9">
         <f t="shared" si="10"/>
-        <v>1.001376323073673</v>
+        <v>1.0054302768806593</v>
       </c>
       <c r="S54" s="7"/>
       <c r="T54" s="7"/>
@@ -17164,50 +17248,57 @@
       <c r="C55" s="47" t="s">
         <v>134</v>
       </c>
-      <c r="D55" s="48"/>
-      <c r="E55" s="48"/>
+      <c r="D55" s="48">
+        <v>-1.4544244920654867</v>
+      </c>
+      <c r="E55" s="48">
+        <v>-2.5464348408255515</v>
+      </c>
       <c r="F55" s="58">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="G55" s="155"/>
-      <c r="H55" s="155"/>
-      <c r="I55" s="55" t="str">
+      <c r="G55" s="125"/>
+      <c r="H55" s="125"/>
+      <c r="I55" s="55">
         <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="J55" s="55" t="str">
+        <v>-2.3030824935597284E-3</v>
+      </c>
+      <c r="J55" s="55">
         <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="K55" s="56" t="str">
+        <v>-5.1860328175829175E-2</v>
+      </c>
+      <c r="K55" s="56">
         <f t="shared" si="22"/>
-        <v/>
-      </c>
-      <c r="L55" s="56" t="str">
+        <v>0.99981177817723821</v>
+      </c>
+      <c r="L55" s="56">
         <f t="shared" si="23"/>
-        <v/>
-      </c>
-      <c r="M55" s="56" t="str">
+        <v>1.1638810253988053E-38</v>
+      </c>
+      <c r="M55" s="56">
         <f t="shared" si="24"/>
-        <v/>
-      </c>
-      <c r="N55" s="56" t="str">
+        <v>1</v>
+      </c>
+      <c r="N55" s="56">
         <f t="shared" si="25"/>
-        <v/>
-      </c>
-      <c r="O55" s="57" t="str">
+        <v>8.3774375489133897E-43</v>
+      </c>
+      <c r="O55" s="57">
         <f t="shared" si="26"/>
-        <v/>
-      </c>
-      <c r="P55" s="57" t="str">
+        <v>1.0053171294409413E-5</v>
+      </c>
+      <c r="P55" s="57">
         <f t="shared" si="27"/>
-        <v/>
-      </c>
-      <c r="Q55" s="57" t="str">
+        <v>8.9216001350038866E-6</v>
+      </c>
+      <c r="Q55" s="57">
         <f t="shared" si="28"/>
-        <v/>
-      </c>
-      <c r="R55" s="7"/>
+        <v>2.8567237254183152E-8</v>
+      </c>
+      <c r="R55" s="9">
+        <f t="shared" si="10"/>
+        <v>1.0053171294409411</v>
+      </c>
       <c r="S55" s="7"/>
       <c r="T55" s="7"/>
       <c r="U55" s="7"/>
@@ -17231,50 +17322,57 @@
       <c r="C56" s="47" t="s">
         <v>136</v>
       </c>
-      <c r="D56" s="48"/>
-      <c r="E56" s="48"/>
+      <c r="D56" s="48">
+        <v>2.3179513188981593</v>
+      </c>
+      <c r="E56" s="48">
+        <v>2.8199025804044244</v>
+      </c>
       <c r="F56" s="58">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="G56" s="155"/>
-      <c r="H56" s="155"/>
-      <c r="I56" s="55" t="str">
+      <c r="G56" s="125"/>
+      <c r="H56" s="125"/>
+      <c r="I56" s="55">
         <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="J56" s="55" t="str">
+        <v>0.34339087488914094</v>
+      </c>
+      <c r="J56" s="55">
         <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="K56" s="56" t="str">
+        <v>1.5460467740842241</v>
+      </c>
+      <c r="K56" s="56">
         <f t="shared" si="22"/>
-        <v/>
-      </c>
-      <c r="L56" s="56" t="str">
+        <v>0.45104958879290064</v>
+      </c>
+      <c r="L56" s="56">
         <f t="shared" si="23"/>
-        <v/>
-      </c>
-      <c r="M56" s="56" t="str">
+        <v>2.0802797084327552E-37</v>
+      </c>
+      <c r="M56" s="56">
         <f t="shared" si="24"/>
-        <v/>
-      </c>
-      <c r="N56" s="56" t="str">
+        <v>1</v>
+      </c>
+      <c r="N56" s="56">
         <f t="shared" si="25"/>
-        <v/>
-      </c>
-      <c r="O56" s="57" t="str">
+        <v>8.7852608873106231E-38</v>
+      </c>
+      <c r="O56" s="57">
         <f t="shared" si="26"/>
-        <v/>
-      </c>
-      <c r="P56" s="57" t="str">
+        <v>4.5353324269441877E-6</v>
+      </c>
+      <c r="P56" s="57">
         <f t="shared" si="27"/>
-        <v/>
-      </c>
-      <c r="Q56" s="57" t="str">
+        <v>1.5946151988550637E-4</v>
+      </c>
+      <c r="Q56" s="57">
         <f t="shared" si="28"/>
-        <v/>
-      </c>
-      <c r="R56" s="7"/>
+        <v>2.9957923367659213E-3</v>
+      </c>
+      <c r="R56" s="9">
+        <f t="shared" si="10"/>
+        <v>0.45353324269441875</v>
+      </c>
       <c r="S56" s="7"/>
       <c r="T56" s="7"/>
       <c r="U56" s="7"/>
@@ -17298,50 +17396,57 @@
       <c r="C57" s="47" t="s">
         <v>138</v>
       </c>
-      <c r="D57" s="48"/>
-      <c r="E57" s="48"/>
+      <c r="D57" s="48">
+        <v>3.46</v>
+      </c>
+      <c r="E57" s="48">
+        <v>2.6247999825375303</v>
+      </c>
       <c r="F57" s="58">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="G57" s="155"/>
-      <c r="H57" s="155"/>
-      <c r="I57" s="55" t="str">
+      <c r="G57" s="125"/>
+      <c r="H57" s="125"/>
+      <c r="I57" s="55">
         <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="J57" s="55" t="str">
+        <v>1.214803061250403</v>
+      </c>
+      <c r="J57" s="55">
         <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="K57" s="56" t="str">
+        <v>2.4468460345716467</v>
+      </c>
+      <c r="K57" s="56">
         <f t="shared" si="22"/>
-        <v/>
-      </c>
-      <c r="L57" s="56" t="str">
+        <v>6.0647388520417442E-2</v>
+      </c>
+      <c r="L57" s="56">
         <f t="shared" si="23"/>
-        <v/>
-      </c>
-      <c r="M57" s="56" t="str">
+        <v>2.2259161834102073E-37</v>
+      </c>
+      <c r="M57" s="56">
         <f t="shared" si="24"/>
-        <v/>
-      </c>
-      <c r="N57" s="56" t="str">
+        <v>1</v>
+      </c>
+      <c r="N57" s="56">
         <f t="shared" si="25"/>
-        <v/>
-      </c>
-      <c r="O57" s="57" t="str">
+        <v>7.5377178777700013E-39</v>
+      </c>
+      <c r="O57" s="57">
         <f t="shared" si="26"/>
-        <v/>
-      </c>
-      <c r="P57" s="57" t="str">
+        <v>6.0981336553756158E-7</v>
+      </c>
+      <c r="P57" s="57">
         <f t="shared" si="27"/>
-        <v/>
-      </c>
-      <c r="Q57" s="57" t="str">
+        <v>1.7062512137454281E-4</v>
+      </c>
+      <c r="Q57" s="57">
         <f t="shared" si="28"/>
-        <v/>
-      </c>
-      <c r="R57" s="7"/>
+        <v>2.5703775613019464E-4</v>
+      </c>
+      <c r="R57" s="9">
+        <f t="shared" si="10"/>
+        <v>6.0981336553756156E-2</v>
+      </c>
       <c r="S57" s="7"/>
       <c r="T57" s="7"/>
       <c r="U57" s="7"/>
@@ -17364,8 +17469,8 @@
       <c r="D58" s="48"/>
       <c r="E58" s="48"/>
       <c r="F58" s="58"/>
-      <c r="G58" s="155"/>
-      <c r="H58" s="155"/>
+      <c r="G58" s="125"/>
+      <c r="H58" s="125"/>
       <c r="I58" s="55" t="str">
         <f t="shared" si="20"/>
         <v/>
@@ -17425,8 +17530,8 @@
       <c r="D59" s="48"/>
       <c r="E59" s="48"/>
       <c r="F59" s="58"/>
-      <c r="G59" s="155"/>
-      <c r="H59" s="155"/>
+      <c r="G59" s="125"/>
+      <c r="H59" s="125"/>
       <c r="I59" s="55" t="str">
         <f t="shared" si="20"/>
         <v/>
@@ -17486,8 +17591,8 @@
       <c r="D60" s="48"/>
       <c r="E60" s="48"/>
       <c r="F60" s="58"/>
-      <c r="G60" s="155"/>
-      <c r="H60" s="155"/>
+      <c r="G60" s="125"/>
+      <c r="H60" s="125"/>
       <c r="I60" s="55" t="str">
         <f t="shared" si="20"/>
         <v/>
@@ -17547,8 +17652,8 @@
       <c r="D61" s="48"/>
       <c r="E61" s="48"/>
       <c r="F61" s="58"/>
-      <c r="G61" s="155"/>
-      <c r="H61" s="155"/>
+      <c r="G61" s="125"/>
+      <c r="H61" s="125"/>
       <c r="I61" s="55" t="str">
         <f t="shared" si="20"/>
         <v/>
@@ -17608,8 +17713,8 @@
       <c r="D62" s="48"/>
       <c r="E62" s="48"/>
       <c r="F62" s="58"/>
-      <c r="G62" s="155"/>
-      <c r="H62" s="155"/>
+      <c r="G62" s="125"/>
+      <c r="H62" s="125"/>
       <c r="I62" s="55" t="str">
         <f t="shared" si="20"/>
         <v/>
@@ -17669,8 +17774,8 @@
       <c r="D63" s="48"/>
       <c r="E63" s="48"/>
       <c r="F63" s="58"/>
-      <c r="G63" s="155"/>
-      <c r="H63" s="155"/>
+      <c r="G63" s="125"/>
+      <c r="H63" s="125"/>
       <c r="I63" s="55" t="str">
         <f t="shared" si="20"/>
         <v/>
@@ -17730,8 +17835,8 @@
       <c r="D64" s="48"/>
       <c r="E64" s="48"/>
       <c r="F64" s="58"/>
-      <c r="G64" s="155"/>
-      <c r="H64" s="155"/>
+      <c r="G64" s="125"/>
+      <c r="H64" s="125"/>
       <c r="I64" s="55" t="str">
         <f t="shared" si="20"/>
         <v/>
@@ -17791,8 +17896,8 @@
       <c r="D65" s="48"/>
       <c r="E65" s="48"/>
       <c r="F65" s="58"/>
-      <c r="G65" s="155"/>
-      <c r="H65" s="155"/>
+      <c r="G65" s="125"/>
+      <c r="H65" s="125"/>
       <c r="I65" s="55" t="str">
         <f t="shared" si="20"/>
         <v/>
@@ -17852,8 +17957,8 @@
       <c r="D66" s="48"/>
       <c r="E66" s="48"/>
       <c r="F66" s="58"/>
-      <c r="G66" s="155"/>
-      <c r="H66" s="155"/>
+      <c r="G66" s="125"/>
+      <c r="H66" s="125"/>
       <c r="I66" s="55" t="str">
         <f t="shared" si="20"/>
         <v/>
@@ -17913,8 +18018,8 @@
       <c r="D67" s="48"/>
       <c r="E67" s="48"/>
       <c r="F67" s="58"/>
-      <c r="G67" s="155"/>
-      <c r="H67" s="155"/>
+      <c r="G67" s="125"/>
+      <c r="H67" s="125"/>
       <c r="I67" s="55" t="str">
         <f t="shared" si="20"/>
         <v/>
@@ -17974,8 +18079,8 @@
       <c r="D68" s="48"/>
       <c r="E68" s="48"/>
       <c r="F68" s="58"/>
-      <c r="G68" s="155"/>
-      <c r="H68" s="155"/>
+      <c r="G68" s="125"/>
+      <c r="H68" s="125"/>
       <c r="I68" s="55" t="str">
         <f t="shared" si="20"/>
         <v/>
@@ -18035,8 +18140,8 @@
       <c r="D69" s="48"/>
       <c r="E69" s="48"/>
       <c r="F69" s="58"/>
-      <c r="G69" s="155"/>
-      <c r="H69" s="155"/>
+      <c r="G69" s="125"/>
+      <c r="H69" s="125"/>
       <c r="I69" s="55" t="str">
         <f t="shared" si="20"/>
         <v/>
@@ -18091,48 +18196,56 @@
     </row>
     <row r="70" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A70" s="7"/>
-      <c r="B70" s="47"/>
-      <c r="C70" s="47"/>
-      <c r="D70" s="48"/>
-      <c r="E70" s="48"/>
+      <c r="B70" s="47" t="s">
+        <v>115</v>
+      </c>
+      <c r="C70" s="47" t="s">
+        <v>116</v>
+      </c>
+      <c r="D70" s="48">
+        <v>1.6452318246143236</v>
+      </c>
+      <c r="E70" s="48">
+        <v>1.8629354124795308</v>
+      </c>
       <c r="F70" s="58"/>
-      <c r="G70" s="155"/>
-      <c r="H70" s="155"/>
-      <c r="I70" s="55" t="str">
+      <c r="G70" s="125"/>
+      <c r="H70" s="125"/>
+      <c r="I70" s="55">
         <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="J70" s="55" t="str">
+        <v>9.3777909413029201E-2</v>
+      </c>
+      <c r="J70" s="55">
         <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="K70" s="56" t="str">
+        <v>0.82289760622407571</v>
+      </c>
+      <c r="K70" s="56">
         <f t="shared" si="22"/>
-        <v/>
-      </c>
-      <c r="L70" s="56" t="str">
+        <v>0.80137770661001506</v>
+      </c>
+      <c r="L70" s="56">
         <f t="shared" si="23"/>
-        <v/>
-      </c>
-      <c r="M70" s="56" t="str">
+        <v>6.9917441947984675E-38</v>
+      </c>
+      <c r="M70" s="56">
         <f t="shared" si="24"/>
-        <v/>
-      </c>
-      <c r="N70" s="56" t="str">
+        <v>1</v>
+      </c>
+      <c r="N70" s="56">
         <f t="shared" si="25"/>
-        <v/>
-      </c>
-      <c r="O70" s="57" t="str">
+        <v>1.7234570321348053E-38</v>
+      </c>
+      <c r="O70" s="57">
         <f t="shared" si="26"/>
-        <v/>
-      </c>
-      <c r="P70" s="57" t="str">
+        <v>0</v>
+      </c>
+      <c r="P70" s="57">
         <f t="shared" si="27"/>
-        <v/>
-      </c>
-      <c r="Q70" s="57" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="57">
         <f t="shared" si="28"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="R70" s="7"/>
       <c r="S70" s="7"/>
@@ -18152,48 +18265,56 @@
     </row>
     <row r="71" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A71" s="7"/>
-      <c r="B71" s="47"/>
-      <c r="C71" s="47"/>
-      <c r="D71" s="48"/>
-      <c r="E71" s="48"/>
+      <c r="B71" s="47" t="s">
+        <v>87</v>
+      </c>
+      <c r="C71" s="47" t="s">
+        <v>88</v>
+      </c>
+      <c r="D71" s="48">
+        <v>3.3511520000000004</v>
+      </c>
+      <c r="E71" s="48">
+        <v>4.2962190000000007</v>
+      </c>
       <c r="F71" s="58"/>
-      <c r="G71" s="155"/>
-      <c r="H71" s="155"/>
-      <c r="I71" s="55" t="str">
+      <c r="G71" s="125"/>
+      <c r="H71" s="125"/>
+      <c r="I71" s="55">
         <f t="shared" ref="I71:I122" si="29">IF(D71=0,"",LOG($K$15*10^D71+$K$16*10^E71+$K$14))</f>
-        <v/>
-      </c>
-      <c r="J71" s="55" t="str">
+        <v>1.205792825575362</v>
+      </c>
+      <c r="J71" s="55">
         <f t="shared" ref="J71:J122" si="30">IF(D71=0,"",LOG($K$21*10^D71+$K$22*10^E71+$K$20))</f>
-        <v/>
-      </c>
-      <c r="K71" s="56" t="str">
+        <v>2.8163863803871312</v>
+      </c>
+      <c r="K71" s="56">
         <f t="shared" ref="K71:K122" si="31">IF(D71=0,"",1/(1+10^D71*$J$15/$J$14+10^E71*$J$16/$J$14+10^J71*$J$19/$J$14))</f>
-        <v/>
-      </c>
-      <c r="L71" s="56" t="str">
+        <v>6.191877284044519E-2</v>
+      </c>
+      <c r="L71" s="56">
         <f t="shared" ref="L71:L122" si="32">IF(D71=0,"",1/(1+10^I71/10^J71*$J$13/$J$19))</f>
-        <v/>
-      </c>
-      <c r="M71" s="56" t="str">
+        <v>5.321810284825154E-37</v>
+      </c>
+      <c r="M71" s="56">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="N71" s="56" t="str">
+        <v>1</v>
+      </c>
+      <c r="N71" s="56">
         <f t="shared" ref="N71:N122" si="33">IF(D71=0,"",1/(1/10^E71*$J$20/$J$22+10^D71/10^E71*$J$21/$J$22+10^I71/10^E71*$J$13/$J$22+1))</f>
-        <v/>
-      </c>
-      <c r="O71" s="57" t="str">
+        <v>3.6113462656333656E-37</v>
+      </c>
+      <c r="O71" s="57">
         <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="P71" s="57" t="str">
+        <v>0</v>
+      </c>
+      <c r="P71" s="57">
         <f t="shared" ref="P71:P122" si="34">IF(D71=0,"",O71*10^J71)</f>
-        <v/>
-      </c>
-      <c r="Q71" s="57" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="57">
         <f t="shared" ref="Q71:Q122" si="35">IF(D71=0,"",F71*N71*$J$7/$J$22)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="R71" s="7"/>
       <c r="S71" s="7"/>
@@ -18213,48 +18334,56 @@
     </row>
     <row r="72" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A72" s="7"/>
-      <c r="B72" s="47"/>
-      <c r="C72" s="47"/>
-      <c r="D72" s="48"/>
-      <c r="E72" s="48"/>
+      <c r="B72" s="47" t="s">
+        <v>79</v>
+      </c>
+      <c r="C72" s="47" t="s">
+        <v>80</v>
+      </c>
+      <c r="D72" s="48">
+        <v>-0.1223633442417989</v>
+      </c>
+      <c r="E72" s="48">
+        <v>-0.65153095448481257</v>
+      </c>
       <c r="F72" s="58"/>
-      <c r="G72" s="155"/>
-      <c r="H72" s="155"/>
-      <c r="I72" s="55" t="str">
+      <c r="G72" s="125"/>
+      <c r="H72" s="125"/>
+      <c r="I72" s="55">
         <f t="shared" si="29"/>
-        <v/>
-      </c>
-      <c r="J72" s="55" t="str">
+        <v>-6.2092895899633685E-4</v>
+      </c>
+      <c r="J72" s="55">
         <f t="shared" si="30"/>
-        <v/>
-      </c>
-      <c r="K72" s="56" t="str">
+        <v>-1.7911449240931149E-2</v>
+      </c>
+      <c r="K72" s="56">
         <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="L72" s="56" t="str">
+        <v>0.99594669571161965</v>
+      </c>
+      <c r="L72" s="56">
         <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="M72" s="56" t="str">
+        <v>1.2536471375943667E-38</v>
+      </c>
+      <c r="M72" s="56">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="N72" s="56" t="str">
+        <v>1</v>
+      </c>
+      <c r="N72" s="56">
         <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="O72" s="57" t="str">
+        <v>6.5513821305467143E-41</v>
+      </c>
+      <c r="O72" s="57">
         <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="P72" s="57" t="str">
+        <v>0</v>
+      </c>
+      <c r="P72" s="57">
         <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="Q72" s="57" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q72" s="57">
         <f t="shared" si="35"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="R72" s="7"/>
       <c r="S72" s="7"/>
@@ -18274,48 +18403,56 @@
     </row>
     <row r="73" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A73" s="7"/>
-      <c r="B73" s="47"/>
-      <c r="C73" s="47"/>
-      <c r="D73" s="48"/>
-      <c r="E73" s="48"/>
+      <c r="B73" s="47" t="s">
+        <v>81</v>
+      </c>
+      <c r="C73" s="47" t="s">
+        <v>82</v>
+      </c>
+      <c r="D73" s="48">
+        <v>1.8253520000000001</v>
+      </c>
+      <c r="E73" s="48">
+        <v>2.0793489999999997</v>
+      </c>
       <c r="F73" s="58"/>
-      <c r="G73" s="155"/>
-      <c r="H73" s="155"/>
-      <c r="I73" s="55" t="str">
+      <c r="G73" s="125"/>
+      <c r="H73" s="125"/>
+      <c r="I73" s="55">
         <f t="shared" si="29"/>
-        <v/>
-      </c>
-      <c r="J73" s="55" t="str">
+        <v>0.13647749932435757</v>
+      </c>
+      <c r="J73" s="55">
         <f t="shared" si="30"/>
-        <v/>
-      </c>
-      <c r="K73" s="56" t="str">
+        <v>0.99262717207612505</v>
+      </c>
+      <c r="K73" s="56">
         <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="L73" s="56" t="str">
+        <v>0.72633616188126371</v>
+      </c>
+      <c r="L73" s="56">
         <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="M73" s="56" t="str">
+        <v>9.3673232327335039E-38</v>
+      </c>
+      <c r="M73" s="56">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="N73" s="56" t="str">
+        <v>1</v>
+      </c>
+      <c r="N73" s="56">
         <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="O73" s="57" t="str">
+        <v>2.5710732980266424E-38</v>
+      </c>
+      <c r="O73" s="57">
         <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="P73" s="57" t="str">
+        <v>0</v>
+      </c>
+      <c r="P73" s="57">
         <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="Q73" s="57" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="57">
         <f t="shared" si="35"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="R73" s="7"/>
       <c r="S73" s="7"/>
@@ -18335,48 +18472,56 @@
     </row>
     <row r="74" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A74" s="7"/>
-      <c r="B74" s="47"/>
-      <c r="C74" s="47"/>
-      <c r="D74" s="48"/>
-      <c r="E74" s="48"/>
+      <c r="B74" s="47" t="s">
+        <v>83</v>
+      </c>
+      <c r="C74" s="47" t="s">
+        <v>84</v>
+      </c>
+      <c r="D74" s="48">
+        <v>2.848199987724402</v>
+      </c>
+      <c r="E74" s="48">
+        <v>3.5741999825375301</v>
+      </c>
       <c r="F74" s="58"/>
-      <c r="G74" s="155"/>
-      <c r="H74" s="155"/>
-      <c r="I74" s="55" t="str">
+      <c r="G74" s="125"/>
+      <c r="H74" s="125"/>
+      <c r="I74" s="55">
         <f t="shared" si="29"/>
-        <v/>
-      </c>
-      <c r="J74" s="55" t="str">
+        <v>0.72733479513716004</v>
+      </c>
+      <c r="J74" s="55">
         <f t="shared" si="30"/>
-        <v/>
-      </c>
-      <c r="K74" s="56" t="str">
+        <v>2.1792047088105391</v>
+      </c>
+      <c r="K74" s="56">
         <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="L74" s="56" t="str">
+        <v>0.18632896473248875</v>
+      </c>
+      <c r="L74" s="56">
         <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="M74" s="56" t="str">
+        <v>3.69262960592219E-37</v>
+      </c>
+      <c r="M74" s="56">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="N74" s="56" t="str">
+        <v>1</v>
+      </c>
+      <c r="N74" s="56">
         <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="O74" s="57" t="str">
+        <v>2.0611430996366476E-37</v>
+      </c>
+      <c r="O74" s="57">
         <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="P74" s="57" t="str">
+        <v>0</v>
+      </c>
+      <c r="P74" s="57">
         <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="Q74" s="57" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="57">
         <f t="shared" si="35"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="R74" s="7"/>
       <c r="S74" s="7"/>
@@ -18396,48 +18541,56 @@
     </row>
     <row r="75" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A75" s="7"/>
-      <c r="B75" s="47"/>
-      <c r="C75" s="47"/>
-      <c r="D75" s="48"/>
-      <c r="E75" s="48"/>
+      <c r="B75" s="47" t="s">
+        <v>85</v>
+      </c>
+      <c r="C75" s="47" t="s">
+        <v>86</v>
+      </c>
+      <c r="D75" s="48">
+        <v>-0.98996462433878363</v>
+      </c>
+      <c r="E75" s="48">
+        <v>-1.885724324763622</v>
+      </c>
       <c r="F75" s="58"/>
-      <c r="G75" s="155"/>
-      <c r="H75" s="155"/>
-      <c r="I75" s="55" t="str">
+      <c r="G75" s="125"/>
+      <c r="H75" s="125"/>
+      <c r="I75" s="55">
         <f t="shared" si="29"/>
-        <v/>
-      </c>
-      <c r="J75" s="55" t="str">
+        <v>-2.1463428094334056E-3</v>
+      </c>
+      <c r="J75" s="55">
         <f t="shared" si="30"/>
-        <v/>
-      </c>
-      <c r="K75" s="56" t="str">
+        <v>-4.8686976382071145E-2</v>
+      </c>
+      <c r="K75" s="56">
         <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="L75" s="56" t="str">
+        <v>0.99945100475420556</v>
+      </c>
+      <c r="L75" s="56">
         <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="M75" s="56" t="str">
+        <v>1.1719934920763741E-38</v>
+      </c>
+      <c r="M75" s="56">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="N75" s="56" t="str">
+        <v>1</v>
+      </c>
+      <c r="N75" s="56">
         <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="O75" s="57" t="str">
+        <v>3.8341135914917693E-42</v>
+      </c>
+      <c r="O75" s="57">
         <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="P75" s="57" t="str">
+        <v>0</v>
+      </c>
+      <c r="P75" s="57">
         <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="Q75" s="57" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="57">
         <f t="shared" si="35"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="R75" s="7"/>
       <c r="S75" s="7"/>
@@ -18457,48 +18610,56 @@
     </row>
     <row r="76" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A76" s="7"/>
-      <c r="B76" s="47"/>
-      <c r="C76" s="47"/>
-      <c r="D76" s="48"/>
-      <c r="E76" s="48"/>
+      <c r="B76" s="47" t="s">
+        <v>89</v>
+      </c>
+      <c r="C76" s="47" t="s">
+        <v>90</v>
+      </c>
+      <c r="D76" s="48">
+        <v>-7.2373500000194575</v>
+      </c>
+      <c r="E76" s="48">
+        <v>-10.772850000027681</v>
+      </c>
       <c r="F76" s="58"/>
-      <c r="G76" s="155"/>
-      <c r="H76" s="155"/>
-      <c r="I76" s="55" t="str">
+      <c r="G76" s="125"/>
+      <c r="H76" s="125"/>
+      <c r="I76" s="55">
         <f t="shared" si="29"/>
-        <v/>
-      </c>
-      <c r="J76" s="55" t="str">
+        <v>-2.38483375204565E-3</v>
+      </c>
+      <c r="J76" s="55">
         <f t="shared" si="30"/>
-        <v/>
-      </c>
-      <c r="K76" s="56" t="str">
+        <v>-5.3500443514237071E-2</v>
+      </c>
+      <c r="K76" s="56">
         <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="L76" s="56" t="str">
+        <v>0.99999999969041098</v>
+      </c>
+      <c r="L76" s="56">
         <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="M76" s="56" t="str">
+        <v>1.1597121947133718E-38</v>
+      </c>
+      <c r="M76" s="56">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="N76" s="56" t="str">
+        <v>1</v>
+      </c>
+      <c r="N76" s="56">
         <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="O76" s="57" t="str">
+        <v>4.9748248044425739E-51</v>
+      </c>
+      <c r="O76" s="57">
         <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="P76" s="57" t="str">
+        <v>0</v>
+      </c>
+      <c r="P76" s="57">
         <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="Q76" s="57" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q76" s="57">
         <f t="shared" si="35"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="R76" s="7"/>
       <c r="S76" s="7"/>
@@ -18518,48 +18679,56 @@
     </row>
     <row r="77" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A77" s="7"/>
-      <c r="B77" s="47"/>
-      <c r="C77" s="47"/>
-      <c r="D77" s="48"/>
-      <c r="E77" s="48"/>
+      <c r="B77" s="47" t="s">
+        <v>91</v>
+      </c>
+      <c r="C77" s="47" t="s">
+        <v>92</v>
+      </c>
+      <c r="D77" s="48">
+        <v>0.89837073464087869</v>
+      </c>
+      <c r="E77" s="48">
+        <v>0.80049921406660218</v>
+      </c>
       <c r="F77" s="58"/>
-      <c r="G77" s="155"/>
-      <c r="H77" s="155"/>
-      <c r="I77" s="55" t="str">
+      <c r="G77" s="125"/>
+      <c r="H77" s="125"/>
+      <c r="I77" s="55">
         <f t="shared" si="29"/>
-        <v/>
-      </c>
-      <c r="J77" s="55" t="str">
+        <v>1.6033091379554689E-2</v>
+      </c>
+      <c r="J77" s="55">
         <f t="shared" si="30"/>
-        <v/>
-      </c>
-      <c r="K77" s="56" t="str">
+        <v>0.24684621561358433</v>
+      </c>
+      <c r="K77" s="56">
         <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="L77" s="56" t="str">
+        <v>0.95847783622330018</v>
+      </c>
+      <c r="L77" s="56">
         <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="M77" s="56" t="str">
+        <v>2.2196216790399494E-38</v>
+      </c>
+      <c r="M77" s="56">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="N77" s="56" t="str">
+        <v>1</v>
+      </c>
+      <c r="N77" s="56">
         <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="O77" s="57" t="str">
+        <v>1.7852912646800246E-39</v>
+      </c>
+      <c r="O77" s="57">
         <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="P77" s="57" t="str">
+        <v>0</v>
+      </c>
+      <c r="P77" s="57">
         <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="Q77" s="57" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="57">
         <f t="shared" si="35"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="R77" s="7"/>
       <c r="S77" s="7"/>
@@ -18579,48 +18748,56 @@
     </row>
     <row r="78" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A78" s="7"/>
-      <c r="B78" s="47"/>
-      <c r="C78" s="47"/>
-      <c r="D78" s="48"/>
-      <c r="E78" s="48"/>
+      <c r="B78" s="47" t="s">
+        <v>93</v>
+      </c>
+      <c r="C78" s="47" t="s">
+        <v>94</v>
+      </c>
+      <c r="D78" s="48">
+        <v>5.1201999877244022</v>
+      </c>
+      <c r="E78" s="48">
+        <v>6.8061999825375299</v>
+      </c>
       <c r="F78" s="58"/>
       <c r="G78" s="7"/>
       <c r="H78" s="7"/>
-      <c r="I78" s="55" t="str">
+      <c r="I78" s="55">
         <f t="shared" si="29"/>
-        <v/>
-      </c>
-      <c r="J78" s="55" t="str">
+        <v>3.2343164583424695</v>
+      </c>
+      <c r="J78" s="55">
         <f t="shared" si="30"/>
-        <v/>
-      </c>
-      <c r="K78" s="56" t="str">
+        <v>5.1936660384397202</v>
+      </c>
+      <c r="K78" s="56">
         <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="L78" s="56" t="str">
+        <v>5.7982736460576007E-4</v>
+      </c>
+      <c r="L78" s="56">
         <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="M78" s="56" t="str">
+        <v>1.1879971910413874E-36</v>
+      </c>
+      <c r="M78" s="56">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="N78" s="56" t="str">
+        <v>1</v>
+      </c>
+      <c r="N78" s="56">
         <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="O78" s="57" t="str">
+        <v>1.0942750104682087E-36</v>
+      </c>
+      <c r="O78" s="57">
         <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="P78" s="57" t="str">
+        <v>0</v>
+      </c>
+      <c r="P78" s="57">
         <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="Q78" s="57" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q78" s="57">
         <f t="shared" si="35"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="R78" s="7"/>
       <c r="S78" s="7"/>
@@ -18640,48 +18817,56 @@
     </row>
     <row r="79" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A79" s="7"/>
-      <c r="B79" s="47"/>
-      <c r="C79" s="47"/>
-      <c r="D79" s="48"/>
-      <c r="E79" s="48"/>
+      <c r="B79" s="47" t="s">
+        <v>95</v>
+      </c>
+      <c r="C79" s="47" t="s">
+        <v>96</v>
+      </c>
+      <c r="D79" s="48">
+        <v>1.6430320000000003</v>
+      </c>
+      <c r="E79" s="48">
+        <v>1.9699289999999996</v>
+      </c>
       <c r="F79" s="58"/>
       <c r="G79" s="7"/>
       <c r="H79" s="7"/>
-      <c r="I79" s="55" t="str">
+      <c r="I79" s="55">
         <f t="shared" si="29"/>
-        <v/>
-      </c>
-      <c r="J79" s="55" t="str">
+        <v>9.4490273200873776E-2</v>
+      </c>
+      <c r="J79" s="55">
         <f t="shared" si="30"/>
-        <v/>
-      </c>
-      <c r="K79" s="56" t="str">
+        <v>0.85054360152384245</v>
+      </c>
+      <c r="K79" s="56">
         <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="L79" s="56" t="str">
+        <v>0.8000643016661515</v>
+      </c>
+      <c r="L79" s="56">
         <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="M79" s="56" t="str">
+        <v>7.4390788499659386E-38</v>
+      </c>
+      <c r="M79" s="56">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="N79" s="56" t="str">
+        <v>1</v>
+      </c>
+      <c r="N79" s="56">
         <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="O79" s="57" t="str">
+        <v>2.2013124210301922E-38</v>
+      </c>
+      <c r="O79" s="57">
         <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="P79" s="57" t="str">
+        <v>0</v>
+      </c>
+      <c r="P79" s="57">
         <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="Q79" s="57" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q79" s="57">
         <f t="shared" si="35"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="R79" s="7"/>
       <c r="S79" s="7"/>
@@ -18701,48 +18886,56 @@
     </row>
     <row r="80" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A80" s="7"/>
-      <c r="B80" s="47"/>
-      <c r="C80" s="47"/>
-      <c r="D80" s="48"/>
-      <c r="E80" s="48"/>
+      <c r="B80" s="47" t="s">
+        <v>97</v>
+      </c>
+      <c r="C80" s="47" t="s">
+        <v>98</v>
+      </c>
+      <c r="D80" s="48">
+        <v>1.9888079999999992</v>
+      </c>
+      <c r="E80" s="48">
+        <v>1.7269960000000002</v>
+      </c>
       <c r="F80" s="58"/>
       <c r="G80" s="7"/>
       <c r="H80" s="7"/>
-      <c r="I80" s="55" t="str">
+      <c r="I80" s="55">
         <f t="shared" si="29"/>
-        <v/>
-      </c>
-      <c r="J80" s="55" t="str">
+        <v>0.18219557821644855</v>
+      </c>
+      <c r="J80" s="55">
         <f t="shared" si="30"/>
-        <v/>
-      </c>
-      <c r="K80" s="56" t="str">
+        <v>1.0487430475844253</v>
+      </c>
+      <c r="K80" s="56">
         <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="L80" s="56" t="str">
+        <v>0.65376187105460315</v>
+      </c>
+      <c r="L80" s="56">
         <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="M80" s="56" t="str">
+        <v>9.5943001975501094E-38</v>
+      </c>
+      <c r="M80" s="56">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="N80" s="56" t="str">
+        <v>1</v>
+      </c>
+      <c r="N80" s="56">
         <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="O80" s="57" t="str">
+        <v>1.0281189857295004E-38</v>
+      </c>
+      <c r="O80" s="57">
         <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="P80" s="57" t="str">
+        <v>0</v>
+      </c>
+      <c r="P80" s="57">
         <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="Q80" s="57" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q80" s="57">
         <f t="shared" si="35"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="R80" s="7"/>
       <c r="S80" s="7"/>
@@ -18762,48 +18955,56 @@
     </row>
     <row r="81" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A81" s="7"/>
-      <c r="B81" s="47"/>
-      <c r="C81" s="47"/>
-      <c r="D81" s="48"/>
-      <c r="E81" s="48"/>
+      <c r="B81" s="47" t="s">
+        <v>99</v>
+      </c>
+      <c r="C81" s="47" t="s">
+        <v>100</v>
+      </c>
+      <c r="D81" s="48">
+        <v>0.57692000000000121</v>
+      </c>
+      <c r="E81" s="48">
+        <v>0.1355349999999973</v>
+      </c>
       <c r="F81" s="58"/>
       <c r="G81" s="7"/>
       <c r="H81" s="7"/>
-      <c r="I81" s="55" t="str">
+      <c r="I81" s="55">
         <f t="shared" si="29"/>
-        <v/>
-      </c>
-      <c r="J81" s="55" t="str">
+        <v>6.3870952141755781E-3</v>
+      </c>
+      <c r="J81" s="55">
         <f t="shared" si="30"/>
-        <v/>
-      </c>
-      <c r="K81" s="56" t="str">
+        <v>0.10294432946993946</v>
+      </c>
+      <c r="K81" s="56">
         <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="L81" s="56" t="str">
+        <v>0.98000450226117841</v>
+      </c>
+      <c r="L81" s="56">
         <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="M81" s="56" t="str">
+        <v>1.6293825764465145E-38</v>
+      </c>
+      <c r="M81" s="56">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="N81" s="56" t="str">
+        <v>1</v>
+      </c>
+      <c r="N81" s="56">
         <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="O81" s="57" t="str">
+        <v>3.9481247079449561E-40</v>
+      </c>
+      <c r="O81" s="57">
         <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="P81" s="57" t="str">
+        <v>0</v>
+      </c>
+      <c r="P81" s="57">
         <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="Q81" s="57" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q81" s="57">
         <f t="shared" si="35"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="R81" s="7"/>
       <c r="S81" s="7"/>
@@ -18823,48 +19024,56 @@
     </row>
     <row r="82" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A82" s="7"/>
-      <c r="B82" s="47"/>
-      <c r="C82" s="47"/>
-      <c r="D82" s="48"/>
-      <c r="E82" s="48"/>
+      <c r="B82" s="47" t="s">
+        <v>101</v>
+      </c>
+      <c r="C82" s="47" t="s">
+        <v>102</v>
+      </c>
+      <c r="D82" s="48">
+        <v>4.3320999877244022</v>
+      </c>
+      <c r="E82" s="48">
+        <v>5.6850999825375297</v>
+      </c>
       <c r="F82" s="58"/>
       <c r="G82" s="7"/>
       <c r="H82" s="7"/>
-      <c r="I82" s="55" t="str">
+      <c r="I82" s="55">
         <f t="shared" si="29"/>
-        <v/>
-      </c>
-      <c r="J82" s="55" t="str">
+        <v>2.2830290403350468</v>
+      </c>
+      <c r="J82" s="55">
         <f t="shared" si="30"/>
-        <v/>
-      </c>
-      <c r="K82" s="56" t="str">
+        <v>4.1103934248091365</v>
+      </c>
+      <c r="K82" s="56">
         <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="L82" s="56" t="str">
+        <v>5.183058680549182E-3</v>
+      </c>
+      <c r="L82" s="56">
         <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="M82" s="56" t="str">
+        <v>8.7665803595652168E-37</v>
+      </c>
+      <c r="M82" s="56">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="N82" s="56" t="str">
+        <v>1</v>
+      </c>
+      <c r="N82" s="56">
         <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="O82" s="57" t="str">
+        <v>7.4014004047284845E-37</v>
+      </c>
+      <c r="O82" s="57">
         <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="P82" s="57" t="str">
+        <v>0</v>
+      </c>
+      <c r="P82" s="57">
         <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="Q82" s="57" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q82" s="57">
         <f t="shared" si="35"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="R82" s="7"/>
       <c r="S82" s="7"/>
@@ -18884,48 +19093,56 @@
     </row>
     <row r="83" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A83" s="7"/>
-      <c r="B83" s="47"/>
-      <c r="C83" s="47"/>
-      <c r="D83" s="48"/>
-      <c r="E83" s="48"/>
+      <c r="B83" s="47" t="s">
+        <v>103</v>
+      </c>
+      <c r="C83" s="47" t="s">
+        <v>104</v>
+      </c>
+      <c r="D83" s="48">
+        <v>2.713299987724402</v>
+      </c>
+      <c r="E83" s="48">
+        <v>3.3822999825375302</v>
+      </c>
       <c r="F83" s="58"/>
       <c r="G83" s="7"/>
       <c r="H83" s="7"/>
-      <c r="I83" s="55" t="str">
+      <c r="I83" s="55">
         <f t="shared" si="29"/>
-        <v/>
-      </c>
-      <c r="J83" s="55" t="str">
+        <v>0.61535497616766821</v>
+      </c>
+      <c r="J83" s="55">
         <f t="shared" si="30"/>
-        <v/>
-      </c>
-      <c r="K83" s="56" t="str">
+        <v>2.0144079910299482</v>
+      </c>
+      <c r="K83" s="56">
         <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="L83" s="56" t="str">
+        <v>0.24113496584831146</v>
+      </c>
+      <c r="L83" s="56">
         <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="M83" s="56" t="str">
+        <v>3.2697823750520026E-37</v>
+      </c>
+      <c r="M83" s="56">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="N83" s="56" t="str">
+        <v>1</v>
+      </c>
+      <c r="N83" s="56">
         <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="O83" s="57" t="str">
+        <v>1.7146992729043089E-37</v>
+      </c>
+      <c r="O83" s="57">
         <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="P83" s="57" t="str">
+        <v>0</v>
+      </c>
+      <c r="P83" s="57">
         <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="Q83" s="57" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q83" s="57">
         <f t="shared" si="35"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="R83" s="7"/>
       <c r="S83" s="7"/>
@@ -18945,48 +19162,56 @@
     </row>
     <row r="84" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A84" s="7"/>
-      <c r="B84" s="47"/>
-      <c r="C84" s="47"/>
-      <c r="D84" s="48"/>
-      <c r="E84" s="48"/>
+      <c r="B84" s="47" t="s">
+        <v>105</v>
+      </c>
+      <c r="C84" s="47" t="s">
+        <v>106</v>
+      </c>
+      <c r="D84" s="48">
+        <v>3.598704000000001</v>
+      </c>
+      <c r="E84" s="48">
+        <v>4.3131730000000008</v>
+      </c>
       <c r="F84" s="58"/>
       <c r="G84" s="7"/>
       <c r="H84" s="7"/>
-      <c r="I84" s="55" t="str">
+      <c r="I84" s="55">
         <f t="shared" si="29"/>
-        <v/>
-      </c>
-      <c r="J84" s="55" t="str">
+        <v>1.4041054944130613</v>
+      </c>
+      <c r="J84" s="55">
         <f t="shared" si="30"/>
-        <v/>
-      </c>
-      <c r="K84" s="56" t="str">
+        <v>2.9211839291051609</v>
+      </c>
+      <c r="K84" s="56">
         <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="L84" s="56" t="str">
+        <v>3.9220188053725367E-2</v>
+      </c>
+      <c r="L84" s="56">
         <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="M84" s="56" t="str">
+        <v>4.2908592446688025E-37</v>
+      </c>
+      <c r="M84" s="56">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="N84" s="56" t="str">
+        <v>1</v>
+      </c>
+      <c r="N84" s="56">
         <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="O84" s="57" t="str">
+        <v>2.3785400194364081E-37</v>
+      </c>
+      <c r="O84" s="57">
         <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="P84" s="57" t="str">
+        <v>0</v>
+      </c>
+      <c r="P84" s="57">
         <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="Q84" s="57" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="57">
         <f t="shared" si="35"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="R84" s="7"/>
       <c r="S84" s="7"/>
@@ -19006,48 +19231,56 @@
     </row>
     <row r="85" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A85" s="7"/>
-      <c r="B85" s="47"/>
-      <c r="C85" s="47"/>
-      <c r="D85" s="48"/>
-      <c r="E85" s="48"/>
+      <c r="B85" s="47" t="s">
+        <v>107</v>
+      </c>
+      <c r="C85" s="47" t="s">
+        <v>108</v>
+      </c>
+      <c r="D85" s="48">
+        <v>-1.2627122753537208</v>
+      </c>
+      <c r="E85" s="48">
+        <v>-2.2737174621228986</v>
+      </c>
       <c r="F85" s="58"/>
       <c r="G85" s="7"/>
       <c r="H85" s="7"/>
-      <c r="I85" s="55" t="str">
+      <c r="I85" s="55">
         <f t="shared" si="29"/>
-        <v/>
-      </c>
-      <c r="J85" s="55" t="str">
+        <v>-2.2576598370427073E-3</v>
+      </c>
+      <c r="J85" s="55">
         <f t="shared" si="30"/>
-        <v/>
-      </c>
-      <c r="K85" s="56" t="str">
+        <v>-5.0942888713472134E-2</v>
+      </c>
+      <c r="K85" s="56">
         <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="L85" s="56" t="str">
+        <v>0.99970721379975491</v>
+      </c>
+      <c r="L85" s="56">
         <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="M85" s="56" t="str">
+        <v>1.166220321585951E-38</v>
+      </c>
+      <c r="M85" s="56">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="N85" s="56" t="str">
+        <v>1</v>
+      </c>
+      <c r="N85" s="56">
         <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="O85" s="57" t="str">
+        <v>1.5695789116662759E-42</v>
+      </c>
+      <c r="O85" s="57">
         <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="P85" s="57" t="str">
+        <v>0</v>
+      </c>
+      <c r="P85" s="57">
         <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="Q85" s="57" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="57">
         <f t="shared" si="35"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="R85" s="7"/>
       <c r="S85" s="7"/>
@@ -19067,48 +19300,56 @@
     </row>
     <row r="86" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A86" s="7"/>
-      <c r="B86" s="47"/>
-      <c r="C86" s="47"/>
-      <c r="D86" s="48"/>
-      <c r="E86" s="48"/>
+      <c r="B86" s="47" t="s">
+        <v>109</v>
+      </c>
+      <c r="C86" s="47" t="s">
+        <v>110</v>
+      </c>
+      <c r="D86" s="48">
+        <v>2.1582748772295566</v>
+      </c>
+      <c r="E86" s="48">
+        <v>2.5927572197209185</v>
+      </c>
       <c r="F86" s="58"/>
       <c r="G86" s="7"/>
       <c r="H86" s="7"/>
-      <c r="I86" s="55" t="str">
+      <c r="I86" s="55">
         <f t="shared" si="29"/>
-        <v/>
-      </c>
-      <c r="J86" s="55" t="str">
+        <v>0.26057631865908987</v>
+      </c>
+      <c r="J86" s="55">
         <f t="shared" si="30"/>
-        <v/>
-      </c>
-      <c r="K86" s="56" t="str">
+        <v>1.3642805972747696</v>
+      </c>
+      <c r="K86" s="56">
         <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="L86" s="56" t="str">
+        <v>0.54580668108038899</v>
+      </c>
+      <c r="L86" s="56">
         <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="M86" s="56" t="str">
+        <v>1.6564186523571383E-37</v>
+      </c>
+      <c r="M86" s="56">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="N86" s="56" t="str">
+        <v>1</v>
+      </c>
+      <c r="N86" s="56">
         <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="O86" s="57" t="str">
+        <v>6.301208619159645E-38</v>
+      </c>
+      <c r="O86" s="57">
         <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="P86" s="57" t="str">
+        <v>0</v>
+      </c>
+      <c r="P86" s="57">
         <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="Q86" s="57" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="57">
         <f t="shared" si="35"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="R86" s="7"/>
       <c r="S86" s="7"/>
@@ -19128,48 +19369,56 @@
     </row>
     <row r="87" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A87" s="7"/>
-      <c r="B87" s="47"/>
-      <c r="C87" s="47"/>
-      <c r="D87" s="48"/>
-      <c r="E87" s="48"/>
+      <c r="B87" s="47" t="s">
+        <v>111</v>
+      </c>
+      <c r="C87" s="47" t="s">
+        <v>112</v>
+      </c>
+      <c r="D87" s="48">
+        <v>0.51229998772440222</v>
+      </c>
+      <c r="E87" s="48">
+        <v>0.25129998253752994</v>
+      </c>
       <c r="F87" s="58"/>
       <c r="G87" s="7"/>
       <c r="H87" s="7"/>
-      <c r="I87" s="55" t="str">
+      <c r="I87" s="55">
         <f t="shared" si="29"/>
-        <v/>
-      </c>
-      <c r="J87" s="55" t="str">
+        <v>5.2260244794124344E-3</v>
+      </c>
+      <c r="J87" s="55">
         <f t="shared" si="30"/>
-        <v/>
-      </c>
-      <c r="K87" s="56" t="str">
+        <v>8.9237920997135206E-2</v>
+      </c>
+      <c r="K87" s="56">
         <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="L87" s="56" t="str">
+        <v>0.98262801455071158</v>
+      </c>
+      <c r="L87" s="56">
         <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="M87" s="56" t="str">
+        <v>1.5829883919722483E-38</v>
+      </c>
+      <c r="M87" s="56">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="N87" s="56" t="str">
+        <v>1</v>
+      </c>
+      <c r="N87" s="56">
         <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="O87" s="57" t="str">
+        <v>5.1679334855023364E-40</v>
+      </c>
+      <c r="O87" s="57">
         <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="P87" s="57" t="str">
+        <v>0</v>
+      </c>
+      <c r="P87" s="57">
         <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="Q87" s="57" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="57">
         <f t="shared" si="35"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="R87" s="7"/>
       <c r="S87" s="7"/>
@@ -19189,48 +19438,56 @@
     </row>
     <row r="88" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A88" s="7"/>
-      <c r="B88" s="47"/>
-      <c r="C88" s="47"/>
-      <c r="D88" s="48"/>
-      <c r="E88" s="48"/>
+      <c r="B88" s="47" t="s">
+        <v>113</v>
+      </c>
+      <c r="C88" s="47" t="s">
+        <v>114</v>
+      </c>
+      <c r="D88" s="48">
+        <v>0.92271245461153151</v>
+      </c>
+      <c r="E88" s="48">
+        <v>0.83512616782767168</v>
+      </c>
       <c r="F88" s="58"/>
       <c r="G88" s="7"/>
       <c r="H88" s="7"/>
-      <c r="I88" s="55" t="str">
+      <c r="I88" s="55">
         <f t="shared" si="29"/>
-        <v/>
-      </c>
-      <c r="J88" s="55" t="str">
+        <v>1.7082011278319043E-2</v>
+      </c>
+      <c r="J88" s="55">
         <f t="shared" si="30"/>
-        <v/>
-      </c>
-      <c r="K88" s="56" t="str">
+        <v>0.26002821205679144</v>
+      </c>
+      <c r="K88" s="56">
         <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="L88" s="56" t="str">
+        <v>0.95616568767124643</v>
+      </c>
+      <c r="L88" s="56">
         <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="M88" s="56" t="str">
+        <v>2.2825065603970897E-38</v>
+      </c>
+      <c r="M88" s="56">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="N88" s="56" t="str">
+        <v>1</v>
+      </c>
+      <c r="N88" s="56">
         <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="O88" s="57" t="str">
+        <v>1.9287996291863749E-39</v>
+      </c>
+      <c r="O88" s="57">
         <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="P88" s="57" t="str">
+        <v>0</v>
+      </c>
+      <c r="P88" s="57">
         <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="Q88" s="57" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="57">
         <f t="shared" si="35"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="R88" s="7"/>
       <c r="S88" s="7"/>
@@ -19250,48 +19507,56 @@
     </row>
     <row r="89" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A89" s="7"/>
-      <c r="B89" s="47"/>
-      <c r="C89" s="47"/>
-      <c r="D89" s="48"/>
-      <c r="E89" s="48"/>
+      <c r="B89" s="47" t="s">
+        <v>117</v>
+      </c>
+      <c r="C89" s="47" t="s">
+        <v>118</v>
+      </c>
+      <c r="D89" s="48">
+        <v>2.8951366557581992</v>
+      </c>
+      <c r="E89" s="48">
+        <v>3.6409690455151855</v>
+      </c>
       <c r="F89" s="58"/>
       <c r="G89" s="7"/>
       <c r="H89" s="7"/>
-      <c r="I89" s="55" t="str">
+      <c r="I89" s="55">
         <f t="shared" si="29"/>
-        <v/>
-      </c>
-      <c r="J89" s="55" t="str">
+        <v>0.76819655741897375</v>
+      </c>
+      <c r="J89" s="55">
         <f t="shared" si="30"/>
-        <v/>
-      </c>
-      <c r="K89" s="56" t="str">
+        <v>2.2370690409846548</v>
+      </c>
+      <c r="K89" s="56">
         <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="L89" s="56" t="str">
+        <v>0.16959717297231178</v>
+      </c>
+      <c r="L89" s="56">
         <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="M89" s="56" t="str">
+        <v>3.8400627152392865E-37</v>
+      </c>
+      <c r="M89" s="56">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="N89" s="56" t="str">
+        <v>1</v>
+      </c>
+      <c r="N89" s="56">
         <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="O89" s="57" t="str">
+        <v>2.1878394317628946E-37</v>
+      </c>
+      <c r="O89" s="57">
         <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="P89" s="57" t="str">
+        <v>0</v>
+      </c>
+      <c r="P89" s="57">
         <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="Q89" s="57" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q89" s="57">
         <f t="shared" si="35"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="R89" s="7"/>
       <c r="S89" s="7"/>
@@ -19311,48 +19576,56 @@
     </row>
     <row r="90" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A90" s="7"/>
-      <c r="B90" s="47"/>
-      <c r="C90" s="47"/>
-      <c r="D90" s="48"/>
-      <c r="E90" s="48"/>
+      <c r="B90" s="47" t="s">
+        <v>119</v>
+      </c>
+      <c r="C90" s="47" t="s">
+        <v>120</v>
+      </c>
+      <c r="D90" s="48">
+        <v>-1.7616394390778063</v>
+      </c>
+      <c r="E90" s="48">
+        <v>-2.9834589203782875</v>
+      </c>
       <c r="F90" s="58"/>
       <c r="G90" s="7"/>
       <c r="H90" s="7"/>
-      <c r="I90" s="55" t="str">
+      <c r="I90" s="55">
         <f t="shared" si="29"/>
-        <v/>
-      </c>
-      <c r="J90" s="55" t="str">
+        <v>-2.3445592739619139E-3</v>
+      </c>
+      <c r="J90" s="55">
         <f t="shared" si="30"/>
-        <v/>
-      </c>
-      <c r="K90" s="56" t="str">
+        <v>-5.2695197824890877E-2</v>
+      </c>
+      <c r="K90" s="56">
         <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="L90" s="56" t="str">
+        <v>0.99990726857737144</v>
+      </c>
+      <c r="L90" s="56">
         <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="M90" s="56" t="str">
+        <v>1.1617567249874914E-38</v>
+      </c>
+      <c r="M90" s="56">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="N90" s="56" t="str">
+        <v>1</v>
+      </c>
+      <c r="N90" s="56">
         <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="O90" s="57" t="str">
+        <v>3.0628702267738444E-43</v>
+      </c>
+      <c r="O90" s="57">
         <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="P90" s="57" t="str">
+        <v>0</v>
+      </c>
+      <c r="P90" s="57">
         <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="Q90" s="57" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q90" s="57">
         <f t="shared" si="35"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="R90" s="7"/>
       <c r="S90" s="7"/>
@@ -19372,48 +19645,56 @@
     </row>
     <row r="91" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A91" s="7"/>
-      <c r="B91" s="47"/>
-      <c r="C91" s="47"/>
-      <c r="D91" s="48"/>
-      <c r="E91" s="48"/>
+      <c r="B91" s="47" t="s">
+        <v>121</v>
+      </c>
+      <c r="C91" s="47" t="s">
+        <v>122</v>
+      </c>
+      <c r="D91" s="48">
+        <v>1.1365502998865107</v>
+      </c>
+      <c r="E91" s="48">
+        <v>1.1393180322329237</v>
+      </c>
       <c r="F91" s="58"/>
       <c r="G91" s="7"/>
       <c r="H91" s="7"/>
-      <c r="I91" s="55" t="str">
+      <c r="I91" s="55">
         <f t="shared" si="29"/>
-        <v/>
-      </c>
-      <c r="J91" s="55" t="str">
+        <v>2.9194031483758934E-2</v>
+      </c>
+      <c r="J91" s="55">
         <f t="shared" si="30"/>
-        <v/>
-      </c>
-      <c r="K91" s="56" t="str">
+        <v>0.39328086995694733</v>
+      </c>
+      <c r="K91" s="56">
         <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="L91" s="56" t="str">
+        <v>0.92986764082672624</v>
+      </c>
+      <c r="L91" s="56">
         <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="M91" s="56" t="str">
+        <v>3.0168427400567719E-38</v>
+      </c>
+      <c r="M91" s="56">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="N91" s="56" t="str">
+        <v>1</v>
+      </c>
+      <c r="N91" s="56">
         <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="O91" s="57" t="str">
+        <v>3.7789135619754592E-39</v>
+      </c>
+      <c r="O91" s="57">
         <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="P91" s="57" t="str">
+        <v>0</v>
+      </c>
+      <c r="P91" s="57">
         <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="Q91" s="57" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="57">
         <f t="shared" si="35"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="R91" s="7"/>
       <c r="S91" s="7"/>
@@ -19433,48 +19714,56 @@
     </row>
     <row r="92" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A92" s="7"/>
-      <c r="B92" s="47"/>
-      <c r="C92" s="47"/>
-      <c r="D92" s="48"/>
-      <c r="E92" s="48"/>
+      <c r="B92" s="47" t="s">
+        <v>123</v>
+      </c>
+      <c r="C92" s="47" t="s">
+        <v>124</v>
+      </c>
+      <c r="D92" s="48">
+        <v>-0.16497034264114602</v>
+      </c>
+      <c r="E92" s="48">
+        <v>-0.71214090995430623</v>
+      </c>
       <c r="F92" s="58"/>
       <c r="G92" s="7"/>
       <c r="H92" s="7"/>
-      <c r="I92" s="55" t="str">
+      <c r="I92" s="55">
         <f t="shared" si="29"/>
-        <v/>
-      </c>
-      <c r="J92" s="55" t="str">
+        <v>-7.8602359813441847E-4</v>
+      </c>
+      <c r="J92" s="55">
         <f t="shared" si="30"/>
-        <v/>
-      </c>
-      <c r="K92" s="56" t="str">
+        <v>-2.1200499850457272E-2</v>
+      </c>
+      <c r="K92" s="56">
         <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="L92" s="56" t="str">
+        <v>0.99632537129663412</v>
+      </c>
+      <c r="L92" s="56">
         <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="M92" s="56" t="str">
+        <v>1.2446617903648383E-38</v>
+      </c>
+      <c r="M92" s="56">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="N92" s="56" t="str">
+        <v>1</v>
+      </c>
+      <c r="N92" s="56">
         <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="O92" s="57" t="str">
+        <v>5.7001734499215699E-41</v>
+      </c>
+      <c r="O92" s="57">
         <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="P92" s="57" t="str">
+        <v>0</v>
+      </c>
+      <c r="P92" s="57">
         <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="Q92" s="57" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="57">
         <f t="shared" si="35"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="R92" s="7"/>
       <c r="S92" s="7"/>
@@ -19494,48 +19783,56 @@
     </row>
     <row r="93" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A93" s="7"/>
-      <c r="B93" s="47"/>
-      <c r="C93" s="47"/>
-      <c r="D93" s="48"/>
-      <c r="E93" s="48"/>
+      <c r="B93" s="47" t="s">
+        <v>125</v>
+      </c>
+      <c r="C93" s="47" t="s">
+        <v>126</v>
+      </c>
+      <c r="D93" s="48">
+        <v>-2.7256879443499291</v>
+      </c>
+      <c r="E93" s="48">
+        <v>-4.3548518644977863</v>
+      </c>
       <c r="F93" s="58"/>
       <c r="G93" s="7"/>
       <c r="H93" s="7"/>
-      <c r="I93" s="55" t="str">
+      <c r="I93" s="55">
         <f t="shared" si="29"/>
-        <v/>
-      </c>
-      <c r="J93" s="55" t="str">
+        <v>-2.3804634030245649E-3</v>
+      </c>
+      <c r="J93" s="55">
         <f t="shared" si="30"/>
-        <v/>
-      </c>
-      <c r="K93" s="56" t="str">
+        <v>-5.341365756501526E-2</v>
+      </c>
+      <c r="K93" s="56">
         <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="L93" s="56" t="str">
+        <v>0.99998993664053948</v>
+      </c>
+      <c r="L93" s="56">
         <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="M93" s="56" t="str">
+        <v>1.1599322929417573E-38</v>
+      </c>
+      <c r="M93" s="56">
         <f t="shared" ref="M93:M127" si="36">IF(D93=0,"",1-L93)</f>
-        <v/>
-      </c>
-      <c r="N93" s="56" t="str">
+        <v>1</v>
+      </c>
+      <c r="N93" s="56">
         <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="O93" s="57" t="str">
+        <v>1.3024814783649132E-44</v>
+      </c>
+      <c r="O93" s="57">
         <f t="shared" ref="O93:O127" si="37">IF(D93=0,"",F93*K93*$J$7/$J$14)</f>
-        <v/>
-      </c>
-      <c r="P93" s="57" t="str">
+        <v>0</v>
+      </c>
+      <c r="P93" s="57">
         <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="Q93" s="57" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="57">
         <f t="shared" si="35"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="R93" s="7"/>
       <c r="S93" s="7"/>
@@ -19555,48 +19852,56 @@
     </row>
     <row r="94" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A94" s="7"/>
-      <c r="B94" s="47"/>
-      <c r="C94" s="47"/>
-      <c r="D94" s="48"/>
-      <c r="E94" s="48"/>
+      <c r="B94" s="47" t="s">
+        <v>127</v>
+      </c>
+      <c r="C94" s="47" t="s">
+        <v>128</v>
+      </c>
+      <c r="D94" s="48">
+        <v>-0.21545001227559774</v>
+      </c>
+      <c r="E94" s="48">
+        <v>-0.78395001746247006</v>
+      </c>
       <c r="F94" s="58"/>
       <c r="G94" s="7"/>
       <c r="H94" s="7"/>
-      <c r="I94" s="55" t="str">
+      <c r="I94" s="55">
         <f t="shared" si="29"/>
-        <v/>
-      </c>
-      <c r="J94" s="55" t="str">
+        <v>-9.6174866178574947E-4</v>
+      </c>
+      <c r="J94" s="55">
         <f t="shared" si="30"/>
-        <v/>
-      </c>
-      <c r="K94" s="56" t="str">
+        <v>-2.4715317794995736E-2</v>
+      </c>
+      <c r="K94" s="56">
         <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="L94" s="56" t="str">
+        <v>0.99672858794301522</v>
+      </c>
+      <c r="L94" s="56">
         <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="M94" s="56" t="str">
+        <v>1.2351288457676123E-38</v>
+      </c>
+      <c r="M94" s="56">
         <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="N94" s="56" t="str">
+        <v>1</v>
+      </c>
+      <c r="N94" s="56">
         <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="O94" s="57" t="str">
+        <v>4.833421710928081E-41</v>
+      </c>
+      <c r="O94" s="57">
         <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="P94" s="57" t="str">
+        <v>0</v>
+      </c>
+      <c r="P94" s="57">
         <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="Q94" s="57" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="57">
         <f t="shared" si="35"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="R94" s="7"/>
       <c r="S94" s="7"/>
@@ -19616,48 +19921,56 @@
     </row>
     <row r="95" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A95" s="7"/>
-      <c r="B95" s="47"/>
-      <c r="C95" s="47"/>
-      <c r="D95" s="48"/>
-      <c r="E95" s="48"/>
+      <c r="B95" s="47" t="s">
+        <v>129</v>
+      </c>
+      <c r="C95" s="47" t="s">
+        <v>130</v>
+      </c>
+      <c r="D95" s="48">
+        <v>1.0310160000000004</v>
+      </c>
+      <c r="E95" s="48">
+        <v>0.78085199999999966</v>
+      </c>
       <c r="F95" s="58"/>
       <c r="G95" s="7"/>
       <c r="H95" s="7"/>
-      <c r="I95" s="55" t="str">
+      <c r="I95" s="55">
         <f t="shared" si="29"/>
-        <v/>
-      </c>
-      <c r="J95" s="55" t="str">
+        <v>2.2261664095594637E-2</v>
+      </c>
+      <c r="J95" s="55">
         <f t="shared" si="30"/>
-        <v/>
-      </c>
-      <c r="K95" s="56" t="str">
+        <v>0.30604318571697814</v>
+      </c>
+      <c r="K95" s="56">
         <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="L95" s="56" t="str">
+        <v>0.94482962490550471</v>
+      </c>
+      <c r="L95" s="56">
         <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="M95" s="56" t="str">
+        <v>2.5075370307450967E-38</v>
+      </c>
+      <c r="M95" s="56">
         <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="N95" s="56" t="str">
+        <v>1</v>
+      </c>
+      <c r="N95" s="56">
         <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="O95" s="57" t="str">
+        <v>1.6820282796103886E-39</v>
+      </c>
+      <c r="O95" s="57">
         <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="P95" s="57" t="str">
+        <v>0</v>
+      </c>
+      <c r="P95" s="57">
         <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="Q95" s="57" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q95" s="57">
         <f t="shared" si="35"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="R95" s="7"/>
       <c r="S95" s="7"/>
@@ -19677,48 +19990,56 @@
     </row>
     <row r="96" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A96" s="7"/>
-      <c r="B96" s="47"/>
-      <c r="C96" s="47"/>
-      <c r="D96" s="48"/>
-      <c r="E96" s="48"/>
+      <c r="B96" s="47" t="s">
+        <v>131</v>
+      </c>
+      <c r="C96" s="47" t="s">
+        <v>132</v>
+      </c>
+      <c r="D96" s="48">
+        <v>-1.8497486811018407</v>
+      </c>
+      <c r="E96" s="48">
+        <v>-3.1087974195955765</v>
+      </c>
       <c r="F96" s="58"/>
       <c r="G96" s="7"/>
       <c r="H96" s="7"/>
-      <c r="I96" s="55" t="str">
+      <c r="I96" s="55">
         <f t="shared" si="29"/>
-        <v/>
-      </c>
-      <c r="J96" s="55" t="str">
+        <v>-2.3519591536599349E-3</v>
+      </c>
+      <c r="J96" s="55">
         <f t="shared" si="30"/>
-        <v/>
-      </c>
-      <c r="K96" s="56" t="str">
+        <v>-5.2843716247280528E-2</v>
+      </c>
+      <c r="K96" s="56">
         <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="L96" s="56" t="str">
+        <v>0.99992430599516557</v>
+      </c>
+      <c r="L96" s="56">
         <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="M96" s="56" t="str">
+        <v>1.1613792880415833E-38</v>
+      </c>
+      <c r="M96" s="56">
         <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="N96" s="56" t="str">
+        <v>1</v>
+      </c>
+      <c r="N96" s="56">
         <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="O96" s="57" t="str">
+        <v>2.2950782479899897E-43</v>
+      </c>
+      <c r="O96" s="57">
         <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="P96" s="57" t="str">
+        <v>0</v>
+      </c>
+      <c r="P96" s="57">
         <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="Q96" s="57" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="57">
         <f t="shared" si="35"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="R96" s="7"/>
       <c r="S96" s="7"/>
@@ -19738,48 +20059,56 @@
     </row>
     <row r="97" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A97" s="7"/>
-      <c r="B97" s="47"/>
-      <c r="C97" s="47"/>
-      <c r="D97" s="48"/>
-      <c r="E97" s="48"/>
+      <c r="B97" s="47" t="s">
+        <v>133</v>
+      </c>
+      <c r="C97" s="47" t="s">
+        <v>134</v>
+      </c>
+      <c r="D97" s="48">
+        <v>-1.4544244920654867</v>
+      </c>
+      <c r="E97" s="48">
+        <v>-2.5464348408255515</v>
+      </c>
       <c r="F97" s="58"/>
       <c r="G97" s="7"/>
       <c r="H97" s="7"/>
-      <c r="I97" s="55" t="str">
+      <c r="I97" s="55">
         <f t="shared" si="29"/>
-        <v/>
-      </c>
-      <c r="J97" s="55" t="str">
+        <v>-2.3030824935597284E-3</v>
+      </c>
+      <c r="J97" s="55">
         <f t="shared" si="30"/>
-        <v/>
-      </c>
-      <c r="K97" s="56" t="str">
+        <v>-5.1860328175829175E-2</v>
+      </c>
+      <c r="K97" s="56">
         <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="L97" s="56" t="str">
+        <v>0.99981177817723821</v>
+      </c>
+      <c r="L97" s="56">
         <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="M97" s="56" t="str">
+        <v>1.1638810253988053E-38</v>
+      </c>
+      <c r="M97" s="56">
         <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="N97" s="56" t="str">
+        <v>1</v>
+      </c>
+      <c r="N97" s="56">
         <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="O97" s="57" t="str">
+        <v>8.3774375489133897E-43</v>
+      </c>
+      <c r="O97" s="57">
         <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="P97" s="57" t="str">
+        <v>0</v>
+      </c>
+      <c r="P97" s="57">
         <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="Q97" s="57" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="57">
         <f t="shared" si="35"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="R97" s="7"/>
       <c r="S97" s="7"/>
@@ -19799,48 +20128,56 @@
     </row>
     <row r="98" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A98" s="7"/>
-      <c r="B98" s="47"/>
-      <c r="C98" s="47"/>
-      <c r="D98" s="48"/>
-      <c r="E98" s="48"/>
+      <c r="B98" s="47" t="s">
+        <v>135</v>
+      </c>
+      <c r="C98" s="47" t="s">
+        <v>136</v>
+      </c>
+      <c r="D98" s="48">
+        <v>2.3179513188981593</v>
+      </c>
+      <c r="E98" s="48">
+        <v>2.8199025804044244</v>
+      </c>
       <c r="F98" s="58"/>
       <c r="G98" s="7"/>
       <c r="H98" s="7"/>
-      <c r="I98" s="55" t="str">
+      <c r="I98" s="55">
         <f t="shared" si="29"/>
-        <v/>
-      </c>
-      <c r="J98" s="55" t="str">
+        <v>0.34339087488914094</v>
+      </c>
+      <c r="J98" s="55">
         <f t="shared" si="30"/>
-        <v/>
-      </c>
-      <c r="K98" s="56" t="str">
+        <v>1.5460467740842241</v>
+      </c>
+      <c r="K98" s="56">
         <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="L98" s="56" t="str">
+        <v>0.45104958879290064</v>
+      </c>
+      <c r="L98" s="56">
         <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="M98" s="56" t="str">
+        <v>2.0802797084327552E-37</v>
+      </c>
+      <c r="M98" s="56">
         <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="N98" s="56" t="str">
+        <v>1</v>
+      </c>
+      <c r="N98" s="56">
         <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="O98" s="57" t="str">
+        <v>8.7852608873106231E-38</v>
+      </c>
+      <c r="O98" s="57">
         <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="P98" s="57" t="str">
+        <v>0</v>
+      </c>
+      <c r="P98" s="57">
         <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="Q98" s="57" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="57">
         <f t="shared" si="35"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="R98" s="7"/>
       <c r="S98" s="7"/>
@@ -19860,48 +20197,56 @@
     </row>
     <row r="99" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A99" s="7"/>
-      <c r="B99" s="47"/>
-      <c r="C99" s="47"/>
-      <c r="D99" s="48"/>
-      <c r="E99" s="48"/>
+      <c r="B99" s="47" t="s">
+        <v>137</v>
+      </c>
+      <c r="C99" s="47" t="s">
+        <v>138</v>
+      </c>
+      <c r="D99" s="48">
+        <v>3.46</v>
+      </c>
+      <c r="E99" s="48">
+        <v>2.6247999825375303</v>
+      </c>
       <c r="F99" s="58"/>
       <c r="G99" s="7"/>
       <c r="H99" s="7"/>
-      <c r="I99" s="55" t="str">
+      <c r="I99" s="55">
         <f t="shared" si="29"/>
-        <v/>
-      </c>
-      <c r="J99" s="55" t="str">
+        <v>1.214803061250403</v>
+      </c>
+      <c r="J99" s="55">
         <f t="shared" si="30"/>
-        <v/>
-      </c>
-      <c r="K99" s="56" t="str">
+        <v>2.4468460345716467</v>
+      </c>
+      <c r="K99" s="56">
         <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="L99" s="56" t="str">
+        <v>6.0647388520417442E-2</v>
+      </c>
+      <c r="L99" s="56">
         <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="M99" s="56" t="str">
+        <v>2.2259161834102073E-37</v>
+      </c>
+      <c r="M99" s="56">
         <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="N99" s="56" t="str">
+        <v>1</v>
+      </c>
+      <c r="N99" s="56">
         <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="O99" s="57" t="str">
+        <v>7.5377178777700013E-39</v>
+      </c>
+      <c r="O99" s="57">
         <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="P99" s="57" t="str">
+        <v>0</v>
+      </c>
+      <c r="P99" s="57">
         <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="Q99" s="57" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="57">
         <f t="shared" si="35"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="R99" s="7"/>
       <c r="S99" s="7"/>
@@ -25237,21 +25582,27 @@
     </row>
   </sheetData>
   <mergeCells count="52">
-    <mergeCell ref="L8:Q8"/>
-    <mergeCell ref="L9:Q9"/>
-    <mergeCell ref="P26:P27"/>
-    <mergeCell ref="I24:Q25"/>
-    <mergeCell ref="I23:Q23"/>
-    <mergeCell ref="Q26:Q27"/>
-    <mergeCell ref="I26:I27"/>
-    <mergeCell ref="J26:J27"/>
-    <mergeCell ref="O26:O27"/>
-    <mergeCell ref="K26:K27"/>
-    <mergeCell ref="L10:Q10"/>
-    <mergeCell ref="I11:Q11"/>
-    <mergeCell ref="L12:Q12"/>
-    <mergeCell ref="L13:Q13"/>
-    <mergeCell ref="M26:M27"/>
+    <mergeCell ref="I2:Q4"/>
+    <mergeCell ref="I5:Q5"/>
+    <mergeCell ref="B23:F23"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="B19:F19"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B8:F10"/>
+    <mergeCell ref="B11:F12"/>
+    <mergeCell ref="E26:E27"/>
+    <mergeCell ref="F26:F27"/>
+    <mergeCell ref="L19:Q19"/>
+    <mergeCell ref="L20:Q20"/>
+    <mergeCell ref="L21:Q21"/>
     <mergeCell ref="B20:C20"/>
     <mergeCell ref="L14:Q14"/>
     <mergeCell ref="L15:Q15"/>
@@ -25268,27 +25619,21 @@
     <mergeCell ref="I17:Q17"/>
     <mergeCell ref="B26:B27"/>
     <mergeCell ref="D26:D27"/>
-    <mergeCell ref="E26:E27"/>
-    <mergeCell ref="F26:F27"/>
-    <mergeCell ref="L19:Q19"/>
-    <mergeCell ref="L20:Q20"/>
-    <mergeCell ref="L21:Q21"/>
-    <mergeCell ref="I2:Q4"/>
-    <mergeCell ref="I5:Q5"/>
-    <mergeCell ref="B23:F23"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="B19:F19"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B8:F10"/>
-    <mergeCell ref="B11:F12"/>
+    <mergeCell ref="L8:Q8"/>
+    <mergeCell ref="L9:Q9"/>
+    <mergeCell ref="P26:P27"/>
+    <mergeCell ref="I24:Q25"/>
+    <mergeCell ref="I23:Q23"/>
+    <mergeCell ref="Q26:Q27"/>
+    <mergeCell ref="I26:I27"/>
+    <mergeCell ref="J26:J27"/>
+    <mergeCell ref="O26:O27"/>
+    <mergeCell ref="K26:K27"/>
+    <mergeCell ref="L10:Q10"/>
+    <mergeCell ref="I11:Q11"/>
+    <mergeCell ref="L12:Q12"/>
+    <mergeCell ref="L13:Q13"/>
+    <mergeCell ref="M26:M27"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
